--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4437"/>
+  <dimension ref="A1:C4503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66973,6 +66973,996 @@
         <v>21</v>
       </c>
     </row>
+    <row r="4438">
+      <c r="A4438" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4438" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C4438" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4439">
+      <c r="A4439" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4439" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C4439" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4440">
+      <c r="A4440" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4440" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C4440" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4441">
+      <c r="A4441" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4441" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C4441" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="4442">
+      <c r="A4442" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4442" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C4442" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="4443">
+      <c r="A4443" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4443" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C4443" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="4444">
+      <c r="A4444" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4444" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C4444" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4445">
+      <c r="A4445" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4445" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C4445" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4446">
+      <c r="A4446" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4446" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C4446" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="4447">
+      <c r="A4447" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4447" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C4447" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="4448">
+      <c r="A4448" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4448" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C4448" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4449">
+      <c r="A4449" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4449" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C4449" t="n">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="4450">
+      <c r="A4450" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4450" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4450" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="4451">
+      <c r="A4451" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4451" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C4451" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="4452">
+      <c r="A4452" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4452" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C4452" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="4453">
+      <c r="A4453" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4453" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C4453" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4454">
+      <c r="A4454" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4454" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C4454" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="4455">
+      <c r="A4455" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4455" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C4455" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4456">
+      <c r="A4456" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4456" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C4456" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="4457">
+      <c r="A4457" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4457" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C4457" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4458">
+      <c r="A4458" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4458" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C4458" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4459">
+      <c r="A4459" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4459" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C4459" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4460">
+      <c r="A4460" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4460" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C4460" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="4461">
+      <c r="A4461" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4461" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C4461" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="4462">
+      <c r="A4462" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4462" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C4462" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="4463">
+      <c r="A4463" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4463" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C4463" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="4464">
+      <c r="A4464" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4464" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C4464" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="4465">
+      <c r="A4465" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4465" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C4465" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="4466">
+      <c r="A4466" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4466" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C4466" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="4467">
+      <c r="A4467" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4467" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C4467" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="4468">
+      <c r="A4468" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4468" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C4468" t="n">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="4469">
+      <c r="A4469" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4469" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C4469" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="4470">
+      <c r="A4470" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4470" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C4470" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4471">
+      <c r="A4471" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4471" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4471" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="4472">
+      <c r="A4472" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4472" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C4472" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4473">
+      <c r="A4473" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4473" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C4473" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="4474">
+      <c r="A4474" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4474" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C4474" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="4475">
+      <c r="A4475" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4475" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C4475" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="4476">
+      <c r="A4476" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4476" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C4476" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4477">
+      <c r="A4477" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4477" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C4477" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="4478">
+      <c r="A4478" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4478" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C4478" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="4479">
+      <c r="A4479" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4479" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C4479" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="4480">
+      <c r="A4480" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4480" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4480" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="4481">
+      <c r="A4481" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4481" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C4481" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="4482">
+      <c r="A4482" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4482" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C4482" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="4483">
+      <c r="A4483" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4483" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C4483" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4484">
+      <c r="A4484" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4484" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C4484" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="4485">
+      <c r="A4485" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4485" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4485" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="4486">
+      <c r="A4486" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4486" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C4486" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="4487">
+      <c r="A4487" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4487" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C4487" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4488">
+      <c r="A4488" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4488" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C4488" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="4489">
+      <c r="A4489" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4489" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C4489" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4490">
+      <c r="A4490" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4490" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C4490" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="4491">
+      <c r="A4491" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4491" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C4491" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4492">
+      <c r="A4492" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4492" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C4492" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="4493">
+      <c r="A4493" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4493" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C4493" t="n">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="4494">
+      <c r="A4494" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4494" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4494" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="4495">
+      <c r="A4495" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4495" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C4495" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4496">
+      <c r="A4496" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4496" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C4496" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4497">
+      <c r="A4497" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4497" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C4497" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="4498">
+      <c r="A4498" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4498" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C4498" t="n">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="4499">
+      <c r="A4499" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4499" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4499" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4500">
+      <c r="A4500" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4500" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C4500" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4501">
+      <c r="A4501" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4501" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C4501" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="4502">
+      <c r="A4502" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4502" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4502" t="n">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="4503">
+      <c r="A4503" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B4503" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C4503" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4503"/>
+  <dimension ref="A1:C4569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67963,6 +67963,996 @@
         <v>22.5</v>
       </c>
     </row>
+    <row r="4504">
+      <c r="A4504" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4504" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C4504" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4505">
+      <c r="A4505" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4505" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C4505" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="4506">
+      <c r="A4506" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4506" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C4506" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="4507">
+      <c r="A4507" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4507" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C4507" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4508">
+      <c r="A4508" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4508" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C4508" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4509">
+      <c r="A4509" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4509" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C4509" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="4510">
+      <c r="A4510" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4510" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C4510" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4511">
+      <c r="A4511" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4511" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C4511" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4512">
+      <c r="A4512" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4512" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C4512" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4513">
+      <c r="A4513" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4513" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C4513" t="n">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="4514">
+      <c r="A4514" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4514" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C4514" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="4515">
+      <c r="A4515" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4515" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4515" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="4516">
+      <c r="A4516" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4516" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C4516" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4517">
+      <c r="A4517" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4517" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C4517" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4518">
+      <c r="A4518" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4518" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C4518" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4519">
+      <c r="A4519" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4519" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C4519" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="4520">
+      <c r="A4520" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4520" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C4520" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="4521">
+      <c r="A4521" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4521" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C4521" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="4522">
+      <c r="A4522" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4522" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C4522" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="4523">
+      <c r="A4523" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4523" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C4523" t="n">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="4524">
+      <c r="A4524" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4524" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C4524" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="4525">
+      <c r="A4525" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4525" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C4525" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="4526">
+      <c r="A4526" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4526" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C4526" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="4527">
+      <c r="A4527" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4527" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C4527" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4528">
+      <c r="A4528" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4528" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C4528" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="4529">
+      <c r="A4529" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4529" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C4529" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4530">
+      <c r="A4530" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4530" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C4530" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4531">
+      <c r="A4531" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4531" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C4531" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4532">
+      <c r="A4532" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4532" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C4532" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="4533">
+      <c r="A4533" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4533" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C4533" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4534">
+      <c r="A4534" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4534" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C4534" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="4535">
+      <c r="A4535" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4535" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C4535" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="4536">
+      <c r="A4536" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4536" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C4536" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="4537">
+      <c r="A4537" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4537" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4537" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="4538">
+      <c r="A4538" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4538" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C4538" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="4539">
+      <c r="A4539" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4539" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C4539" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4540">
+      <c r="A4540" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4540" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C4540" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="4541">
+      <c r="A4541" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4541" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C4541" t="n">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="4542">
+      <c r="A4542" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4542" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C4542" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="4543">
+      <c r="A4543" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4543" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C4543" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4544">
+      <c r="A4544" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4544" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C4544" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="4545">
+      <c r="A4545" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4545" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C4545" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4546">
+      <c r="A4546" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4546" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4546" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="4547">
+      <c r="A4547" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4547" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C4547" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4548">
+      <c r="A4548" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4548" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C4548" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="4549">
+      <c r="A4549" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4549" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C4549" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4550">
+      <c r="A4550" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4550" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C4550" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="4551">
+      <c r="A4551" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4551" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4551" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="4552">
+      <c r="A4552" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4552" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C4552" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4553">
+      <c r="A4553" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4553" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C4553" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4554">
+      <c r="A4554" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4554" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C4554" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="4555">
+      <c r="A4555" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4555" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C4555" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="4556">
+      <c r="A4556" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4556" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C4556" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="4557">
+      <c r="A4557" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4557" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C4557" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4558">
+      <c r="A4558" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4558" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C4558" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4559">
+      <c r="A4559" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4559" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C4559" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4560">
+      <c r="A4560" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4560" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4560" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4561">
+      <c r="A4561" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4561" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C4561" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4562">
+      <c r="A4562" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4562" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C4562" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4563">
+      <c r="A4563" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4563" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C4563" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4564">
+      <c r="A4564" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4564" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C4564" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4565">
+      <c r="A4565" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4565" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4565" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4566">
+      <c r="A4566" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4566" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C4566" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4567">
+      <c r="A4567" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4567" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C4567" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="4568">
+      <c r="A4568" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4568" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4568" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4569">
+      <c r="A4569" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B4569" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C4569" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4569"/>
+  <dimension ref="A1:C4636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68953,6 +68953,1011 @@
         <v>21.2</v>
       </c>
     </row>
+    <row r="4570">
+      <c r="A4570" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4570" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C4570" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4571">
+      <c r="A4571" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4571" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C4571" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="4572">
+      <c r="A4572" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4572" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C4572" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4573">
+      <c r="A4573" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4573" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C4573" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="4574">
+      <c r="A4574" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4574" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C4574" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4575">
+      <c r="A4575" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4575" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C4575" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="4576">
+      <c r="A4576" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4576" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C4576" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="4577">
+      <c r="A4577" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4577" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C4577" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="4578">
+      <c r="A4578" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4578" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C4578" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4579">
+      <c r="A4579" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4579" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C4579" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="4580">
+      <c r="A4580" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4580" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C4580" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="4581">
+      <c r="A4581" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4581" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C4581" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="4582">
+      <c r="A4582" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4582" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4582" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="4583">
+      <c r="A4583" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4583" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C4583" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="4584">
+      <c r="A4584" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4584" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C4584" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4585">
+      <c r="A4585" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4585" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C4585" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4586">
+      <c r="A4586" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4586" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C4586" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4587">
+      <c r="A4587" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4587" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C4587" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4588">
+      <c r="A4588" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4588" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C4588" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4589">
+      <c r="A4589" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4589" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C4589" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="4590">
+      <c r="A4590" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4590" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C4590" t="n">
+        <v>35.3</v>
+      </c>
+    </row>
+    <row r="4591">
+      <c r="A4591" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4591" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C4591" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4592">
+      <c r="A4592" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4592" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C4592" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4593">
+      <c r="A4593" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4593" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C4593" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="4594">
+      <c r="A4594" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4594" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C4594" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4595">
+      <c r="A4595" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4595" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C4595" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4596">
+      <c r="A4596" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4596" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C4596" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="4597">
+      <c r="A4597" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4597" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C4597" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4598">
+      <c r="A4598" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4598" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C4598" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="4599">
+      <c r="A4599" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4599" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C4599" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="4600">
+      <c r="A4600" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4600" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C4600" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="4601">
+      <c r="A4601" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4601" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C4601" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="4602">
+      <c r="A4602" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4602" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C4602" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4603">
+      <c r="A4603" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4603" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C4603" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="4604">
+      <c r="A4604" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4604" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4604" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="4605">
+      <c r="A4605" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4605" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C4605" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4606">
+      <c r="A4606" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4606" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C4606" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4607">
+      <c r="A4607" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4607" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C4607" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4608">
+      <c r="A4608" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4608" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C4608" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4609">
+      <c r="A4609" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4609" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C4609" t="n">
+        <v>34.8</v>
+      </c>
+    </row>
+    <row r="4610">
+      <c r="A4610" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4610" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C4610" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="4611">
+      <c r="A4611" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4611" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C4611" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4612">
+      <c r="A4612" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4612" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C4612" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4613">
+      <c r="A4613" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4613" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4613" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="4614">
+      <c r="A4614" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4614" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C4614" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4615">
+      <c r="A4615" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4615" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C4615" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="4616">
+      <c r="A4616" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4616" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C4616" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4617">
+      <c r="A4617" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4617" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C4617" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4618">
+      <c r="A4618" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4618" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4618" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4619">
+      <c r="A4619" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4619" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C4619" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="4620">
+      <c r="A4620" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4620" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C4620" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="4621">
+      <c r="A4621" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4621" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C4621" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4622">
+      <c r="A4622" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4622" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C4622" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="4623">
+      <c r="A4623" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4623" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C4623" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="4624">
+      <c r="A4624" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4624" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C4624" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4625">
+      <c r="A4625" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4625" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C4625" t="n">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="4626">
+      <c r="A4626" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4626" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C4626" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="4627">
+      <c r="A4627" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4627" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4627" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="4628">
+      <c r="A4628" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4628" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C4628" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="4629">
+      <c r="A4629" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4629" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C4629" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4630">
+      <c r="A4630" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4630" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C4630" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="4631">
+      <c r="A4631" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4631" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C4631" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="4632">
+      <c r="A4632" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4632" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4632" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="4633">
+      <c r="A4633" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4633" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C4633" t="n">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="4634">
+      <c r="A4634" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4634" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C4634" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4635">
+      <c r="A4635" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4635" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4635" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="4636">
+      <c r="A4636" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4636" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C4636" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4636"/>
+  <dimension ref="A1:C4703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69958,6 +69958,1011 @@
         <v>23.9</v>
       </c>
     </row>
+    <row r="4637">
+      <c r="A4637" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4637" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C4637" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4638">
+      <c r="A4638" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4638" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C4638" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="4639">
+      <c r="A4639" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4639" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C4639" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4640">
+      <c r="A4640" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4640" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C4640" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="4641">
+      <c r="A4641" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4641" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C4641" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="4642">
+      <c r="A4642" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4642" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C4642" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4643">
+      <c r="A4643" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4643" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C4643" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="4644">
+      <c r="A4644" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4644" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C4644" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4645">
+      <c r="A4645" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4645" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C4645" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="4646">
+      <c r="A4646" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4646" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C4646" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4647">
+      <c r="A4647" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4647" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C4647" t="n">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="4648">
+      <c r="A4648" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4648" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C4648" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="4649">
+      <c r="A4649" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4649" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4649" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="4650">
+      <c r="A4650" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4650" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C4650" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4651">
+      <c r="A4651" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4651" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C4651" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4652">
+      <c r="A4652" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4652" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C4652" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4653">
+      <c r="A4653" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4653" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C4653" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4654">
+      <c r="A4654" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4654" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C4654" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4655">
+      <c r="A4655" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4655" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C4655" t="n">
+        <v>36.2</v>
+      </c>
+    </row>
+    <row r="4656">
+      <c r="A4656" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4656" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C4656" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="4657">
+      <c r="A4657" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4657" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C4657" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4658">
+      <c r="A4658" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4658" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C4658" t="n">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="4659">
+      <c r="A4659" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4659" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C4659" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="4660">
+      <c r="A4660" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4660" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C4660" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="4661">
+      <c r="A4661" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4661" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C4661" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4662">
+      <c r="A4662" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4662" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C4662" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="4663">
+      <c r="A4663" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4663" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C4663" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="4664">
+      <c r="A4664" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4664" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C4664" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4665">
+      <c r="A4665" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4665" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C4665" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="4666">
+      <c r="A4666" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4666" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C4666" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="4667">
+      <c r="A4667" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4667" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C4667" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="4668">
+      <c r="A4668" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4668" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C4668" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="4669">
+      <c r="A4669" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4669" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C4669" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4670">
+      <c r="A4670" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4670" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C4670" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="4671">
+      <c r="A4671" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4671" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4671" t="n">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="4672">
+      <c r="A4672" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4672" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C4672" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="4673">
+      <c r="A4673" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4673" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C4673" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="4674">
+      <c r="A4674" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4674" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C4674" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="4675">
+      <c r="A4675" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4675" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C4675" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4676">
+      <c r="A4676" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4676" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C4676" t="n">
+        <v>34.8</v>
+      </c>
+    </row>
+    <row r="4677">
+      <c r="A4677" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4677" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C4677" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="4678">
+      <c r="A4678" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4678" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C4678" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4679">
+      <c r="A4679" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4679" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C4679" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="4680">
+      <c r="A4680" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4680" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4680" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="4681">
+      <c r="A4681" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4681" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C4681" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="4682">
+      <c r="A4682" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4682" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C4682" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4683">
+      <c r="A4683" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4683" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C4683" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="4684">
+      <c r="A4684" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4684" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C4684" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4685">
+      <c r="A4685" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4685" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4685" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="4686">
+      <c r="A4686" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4686" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C4686" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="4687">
+      <c r="A4687" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4687" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C4687" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4688">
+      <c r="A4688" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4688" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C4688" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="4689">
+      <c r="A4689" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4689" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C4689" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4690">
+      <c r="A4690" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4690" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C4690" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4691">
+      <c r="A4691" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4691" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C4691" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="4692">
+      <c r="A4692" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4692" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C4692" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="4693">
+      <c r="A4693" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4693" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C4693" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="4694">
+      <c r="A4694" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4694" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4694" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4695">
+      <c r="A4695" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4695" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C4695" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4696">
+      <c r="A4696" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4696" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C4696" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4697">
+      <c r="A4697" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4697" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C4697" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="4698">
+      <c r="A4698" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4698" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C4698" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="4699">
+      <c r="A4699" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4699" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4699" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="4700">
+      <c r="A4700" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4700" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C4700" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="4701">
+      <c r="A4701" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4701" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C4701" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4702">
+      <c r="A4702" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4702" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4702" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4703">
+      <c r="A4703" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B4703" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C4703" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4703"/>
+  <dimension ref="A1:C4768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70963,6 +70963,981 @@
         <v>22.8</v>
       </c>
     </row>
+    <row r="4704">
+      <c r="A4704" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4704" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C4704" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4705">
+      <c r="A4705" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4705" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C4705" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="4706">
+      <c r="A4706" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4706" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C4706" t="n">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="4707">
+      <c r="A4707" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4707" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C4707" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="4708">
+      <c r="A4708" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4708" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C4708" t="n">
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="4709">
+      <c r="A4709" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4709" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C4709" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="4710">
+      <c r="A4710" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4710" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C4710" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4711">
+      <c r="A4711" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4711" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C4711" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="4712">
+      <c r="A4712" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4712" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C4712" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="4713">
+      <c r="A4713" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4713" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C4713" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="4714">
+      <c r="A4714" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4714" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C4714" t="n">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="4715">
+      <c r="A4715" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4715" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C4715" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="4716">
+      <c r="A4716" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4716" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4716" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="4717">
+      <c r="A4717" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4717" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C4717" t="n">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="4718">
+      <c r="A4718" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4718" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C4718" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4719">
+      <c r="A4719" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4719" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C4719" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4720">
+      <c r="A4720" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4720" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C4720" t="n">
+        <v>35.2</v>
+      </c>
+    </row>
+    <row r="4721">
+      <c r="A4721" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4721" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C4721" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="4722">
+      <c r="A4722" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4722" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C4722" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4723">
+      <c r="A4723" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4723" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C4723" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="4724">
+      <c r="A4724" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4724" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C4724" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="4725">
+      <c r="A4725" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4725" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C4725" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4726">
+      <c r="A4726" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4726" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C4726" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="4727">
+      <c r="A4727" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4727" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C4727" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="4728">
+      <c r="A4728" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4728" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C4728" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="4729">
+      <c r="A4729" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4729" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C4729" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4730">
+      <c r="A4730" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4730" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C4730" t="n">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="4731">
+      <c r="A4731" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4731" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C4731" t="n">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="4732">
+      <c r="A4732" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4732" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C4732" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="4733">
+      <c r="A4733" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4733" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C4733" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="4734">
+      <c r="A4734" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4734" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C4734" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4735">
+      <c r="A4735" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4735" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C4735" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4736">
+      <c r="A4736" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4736" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4736" t="n">
+        <v>37.2</v>
+      </c>
+    </row>
+    <row r="4737">
+      <c r="A4737" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4737" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C4737" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="4738">
+      <c r="A4738" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4738" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C4738" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="4739">
+      <c r="A4739" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4739" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C4739" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4740">
+      <c r="A4740" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4740" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C4740" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="4741">
+      <c r="A4741" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4741" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C4741" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4742">
+      <c r="A4742" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4742" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C4742" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4743">
+      <c r="A4743" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4743" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C4743" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="4744">
+      <c r="A4744" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4744" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C4744" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="4745">
+      <c r="A4745" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4745" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4745" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="4746">
+      <c r="A4746" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4746" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C4746" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="4747">
+      <c r="A4747" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4747" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C4747" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="4748">
+      <c r="A4748" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4748" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C4748" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="4749">
+      <c r="A4749" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4749" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C4749" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="4750">
+      <c r="A4750" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4750" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4750" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4751">
+      <c r="A4751" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4751" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C4751" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="4752">
+      <c r="A4752" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4752" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C4752" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4753">
+      <c r="A4753" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4753" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C4753" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4754">
+      <c r="A4754" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4754" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C4754" t="n">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="4755">
+      <c r="A4755" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4755" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C4755" t="n">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="4756">
+      <c r="A4756" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4756" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C4756" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="4757">
+      <c r="A4757" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4757" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C4757" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4758">
+      <c r="A4758" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4758" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C4758" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="4759">
+      <c r="A4759" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4759" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4759" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="4760">
+      <c r="A4760" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4760" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C4760" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="4761">
+      <c r="A4761" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4761" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C4761" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="4762">
+      <c r="A4762" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4762" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C4762" t="n">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="4763">
+      <c r="A4763" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4763" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C4763" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="4764">
+      <c r="A4764" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4764" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4764" t="n">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="4765">
+      <c r="A4765" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4765" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C4765" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="4766">
+      <c r="A4766" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4766" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C4766" t="n">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="4767">
+      <c r="A4767" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4767" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4767" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="4768">
+      <c r="A4768" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4768" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C4768" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4768"/>
+  <dimension ref="A1:C4833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71938,6 +71938,981 @@
         <v>20.1</v>
       </c>
     </row>
+    <row r="4769">
+      <c r="A4769" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4769" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C4769" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4770">
+      <c r="A4770" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4770" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C4770" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="4771">
+      <c r="A4771" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4771" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C4771" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="4772">
+      <c r="A4772" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4772" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C4772" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="4773">
+      <c r="A4773" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4773" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C4773" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="4774">
+      <c r="A4774" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4774" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C4774" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="4775">
+      <c r="A4775" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4775" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C4775" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="4776">
+      <c r="A4776" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4776" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C4776" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="4777">
+      <c r="A4777" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4777" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C4777" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="4778">
+      <c r="A4778" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4778" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C4778" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="4779">
+      <c r="A4779" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4779" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C4779" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="4780">
+      <c r="A4780" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4780" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C4780" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4781">
+      <c r="A4781" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4781" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4781" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="4782">
+      <c r="A4782" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4782" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C4782" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="4783">
+      <c r="A4783" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4783" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C4783" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="4784">
+      <c r="A4784" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4784" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C4784" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="4785">
+      <c r="A4785" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4785" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C4785" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="4786">
+      <c r="A4786" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4786" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C4786" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="4787">
+      <c r="A4787" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4787" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C4787" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4788">
+      <c r="A4788" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4788" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C4788" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="4789">
+      <c r="A4789" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4789" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C4789" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="4790">
+      <c r="A4790" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4790" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C4790" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4791">
+      <c r="A4791" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4791" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C4791" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4792">
+      <c r="A4792" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4792" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C4792" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="4793">
+      <c r="A4793" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4793" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C4793" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4794">
+      <c r="A4794" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4794" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C4794" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="4795">
+      <c r="A4795" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4795" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C4795" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="4796">
+      <c r="A4796" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4796" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C4796" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="4797">
+      <c r="A4797" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4797" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C4797" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4798">
+      <c r="A4798" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4798" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C4798" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="4799">
+      <c r="A4799" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4799" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C4799" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="4800">
+      <c r="A4800" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4800" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C4800" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4801">
+      <c r="A4801" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4801" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4801" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="4802">
+      <c r="A4802" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4802" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C4802" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4803">
+      <c r="A4803" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4803" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C4803" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="4804">
+      <c r="A4804" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4804" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C4804" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="4805">
+      <c r="A4805" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4805" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C4805" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4806">
+      <c r="A4806" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4806" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C4806" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="4807">
+      <c r="A4807" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4807" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C4807" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="4808">
+      <c r="A4808" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4808" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C4808" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="4809">
+      <c r="A4809" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4809" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C4809" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="4810">
+      <c r="A4810" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4810" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4810" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="4811">
+      <c r="A4811" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4811" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C4811" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="4812">
+      <c r="A4812" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4812" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C4812" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="4813">
+      <c r="A4813" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4813" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C4813" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="4814">
+      <c r="A4814" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4814" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C4814" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4815">
+      <c r="A4815" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4815" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4815" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="4816">
+      <c r="A4816" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4816" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C4816" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="4817">
+      <c r="A4817" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4817" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C4817" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4818">
+      <c r="A4818" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4818" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C4818" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="4819">
+      <c r="A4819" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4819" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C4819" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="4820">
+      <c r="A4820" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4820" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C4820" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="4821">
+      <c r="A4821" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4821" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C4821" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4822">
+      <c r="A4822" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4822" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C4822" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="4823">
+      <c r="A4823" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4823" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C4823" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4824">
+      <c r="A4824" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4824" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4824" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="4825">
+      <c r="A4825" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4825" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C4825" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4826">
+      <c r="A4826" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4826" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C4826" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="4827">
+      <c r="A4827" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4827" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C4827" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="4828">
+      <c r="A4828" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4828" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C4828" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="4829">
+      <c r="A4829" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4829" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4829" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="4830">
+      <c r="A4830" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4830" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C4830" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="4831">
+      <c r="A4831" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4831" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C4831" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="4832">
+      <c r="A4832" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4832" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4832" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="4833">
+      <c r="A4833" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B4833" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C4833" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4833"/>
+  <dimension ref="A1:C4897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72913,6 +72913,966 @@
         <v>15</v>
       </c>
     </row>
+    <row r="4834">
+      <c r="A4834" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4834" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C4834" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4835">
+      <c r="A4835" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4835" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C4835" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="4836">
+      <c r="A4836" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4836" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C4836" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4837">
+      <c r="A4837" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4837" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C4837" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="4838">
+      <c r="A4838" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4838" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C4838" t="n">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="4839">
+      <c r="A4839" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4839" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C4839" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="4840">
+      <c r="A4840" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4840" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C4840" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="4841">
+      <c r="A4841" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4841" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C4841" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="4842">
+      <c r="A4842" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4842" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C4842" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4843">
+      <c r="A4843" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4843" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C4843" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4844">
+      <c r="A4844" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4844" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C4844" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="4845">
+      <c r="A4845" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4845" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C4845" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="4846">
+      <c r="A4846" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4846" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4846" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="4847">
+      <c r="A4847" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4847" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C4847" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4848">
+      <c r="A4848" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4848" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C4848" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="4849">
+      <c r="A4849" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4849" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C4849" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="4850">
+      <c r="A4850" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4850" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C4850" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="4851">
+      <c r="A4851" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4851" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C4851" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="4852">
+      <c r="A4852" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4852" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C4852" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4853">
+      <c r="A4853" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4853" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C4853" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="4854">
+      <c r="A4854" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4854" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C4854" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="4855">
+      <c r="A4855" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4855" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C4855" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4856">
+      <c r="A4856" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4856" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C4856" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="4857">
+      <c r="A4857" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4857" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C4857" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="4858">
+      <c r="A4858" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4858" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C4858" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="4859">
+      <c r="A4859" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4859" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C4859" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="4860">
+      <c r="A4860" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4860" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C4860" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="4861">
+      <c r="A4861" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4861" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C4861" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="4862">
+      <c r="A4862" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4862" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C4862" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="4863">
+      <c r="A4863" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4863" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C4863" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="4864">
+      <c r="A4864" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4864" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C4864" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="4865">
+      <c r="A4865" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4865" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C4865" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="4866">
+      <c r="A4866" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4866" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4866" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="4867">
+      <c r="A4867" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4867" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C4867" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="4868">
+      <c r="A4868" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4868" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C4868" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="4869">
+      <c r="A4869" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4869" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C4869" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="4870">
+      <c r="A4870" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4870" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C4870" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="4871">
+      <c r="A4871" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4871" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C4871" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="4872">
+      <c r="A4872" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4872" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C4872" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="4873">
+      <c r="A4873" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4873" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C4873" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="4874">
+      <c r="A4874" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4874" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4874" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="4875">
+      <c r="A4875" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4875" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C4875" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="4876">
+      <c r="A4876" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4876" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C4876" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="4877">
+      <c r="A4877" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4877" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C4877" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="4878">
+      <c r="A4878" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4878" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C4878" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4879">
+      <c r="A4879" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4879" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4879" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="4880">
+      <c r="A4880" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4880" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C4880" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="4881">
+      <c r="A4881" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4881" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C4881" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4882">
+      <c r="A4882" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4882" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C4882" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4883">
+      <c r="A4883" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4883" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C4883" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4884">
+      <c r="A4884" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4884" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C4884" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="4885">
+      <c r="A4885" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4885" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C4885" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4886">
+      <c r="A4886" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4886" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C4886" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4887">
+      <c r="A4887" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4887" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C4887" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="4888">
+      <c r="A4888" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4888" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4888" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="4889">
+      <c r="A4889" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4889" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C4889" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4890">
+      <c r="A4890" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4890" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C4890" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="4891">
+      <c r="A4891" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4891" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C4891" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="4892">
+      <c r="A4892" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4892" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C4892" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4893">
+      <c r="A4893" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4893" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4893" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="4894">
+      <c r="A4894" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4894" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C4894" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4895">
+      <c r="A4895" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4895" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C4895" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="4896">
+      <c r="A4896" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4896" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4896" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="4897">
+      <c r="A4897" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4897" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C4897" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4897"/>
+  <dimension ref="A1:C4959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73873,6 +73873,936 @@
         <v>12.5</v>
       </c>
     </row>
+    <row r="4898">
+      <c r="A4898" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4898" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C4898" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4899">
+      <c r="A4899" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4899" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C4899" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="4900">
+      <c r="A4900" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4900" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C4900" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="4901">
+      <c r="A4901" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4901" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C4901" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="4902">
+      <c r="A4902" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4902" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C4902" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="4903">
+      <c r="A4903" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4903" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C4903" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="4904">
+      <c r="A4904" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4904" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C4904" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4905">
+      <c r="A4905" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4905" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C4905" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4906">
+      <c r="A4906" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4906" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C4906" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="4907">
+      <c r="A4907" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4907" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C4907" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4908">
+      <c r="A4908" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4908" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C4908" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="4909">
+      <c r="A4909" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4909" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4909" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="4910">
+      <c r="A4910" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4910" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C4910" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="4911">
+      <c r="A4911" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4911" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C4911" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4912">
+      <c r="A4912" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4912" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C4912" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="4913">
+      <c r="A4913" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4913" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C4913" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="4914">
+      <c r="A4914" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4914" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C4914" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="4915">
+      <c r="A4915" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4915" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C4915" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4916">
+      <c r="A4916" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4916" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C4916" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="4917">
+      <c r="A4917" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4917" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C4917" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4918">
+      <c r="A4918" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4918" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C4918" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="4919">
+      <c r="A4919" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4919" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C4919" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4920">
+      <c r="A4920" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4920" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C4920" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="4921">
+      <c r="A4921" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4921" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C4921" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="4922">
+      <c r="A4922" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4922" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C4922" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4923">
+      <c r="A4923" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4923" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C4923" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="4924">
+      <c r="A4924" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4924" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C4924" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="4925">
+      <c r="A4925" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4925" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C4925" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="4926">
+      <c r="A4926" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4926" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C4926" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="4927">
+      <c r="A4927" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4927" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4927" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="4928">
+      <c r="A4928" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4928" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C4928" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="4929">
+      <c r="A4929" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4929" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C4929" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="4930">
+      <c r="A4930" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4930" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C4930" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4931">
+      <c r="A4931" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4931" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C4931" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="4932">
+      <c r="A4932" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4932" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C4932" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="4933">
+      <c r="A4933" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4933" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C4933" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="4934">
+      <c r="A4934" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4934" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C4934" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="4935">
+      <c r="A4935" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4935" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C4935" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="4936">
+      <c r="A4936" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4936" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4936" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4937">
+      <c r="A4937" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4937" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C4937" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="4938">
+      <c r="A4938" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4938" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C4938" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="4939">
+      <c r="A4939" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4939" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C4939" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="4940">
+      <c r="A4940" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4940" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C4940" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="4941">
+      <c r="A4941" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4941" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4941" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="4942">
+      <c r="A4942" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4942" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C4942" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="4943">
+      <c r="A4943" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4943" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C4943" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="4944">
+      <c r="A4944" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4944" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C4944" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="4945">
+      <c r="A4945" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4945" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C4945" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4946">
+      <c r="A4946" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4946" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C4946" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="4947">
+      <c r="A4947" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4947" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C4947" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4948">
+      <c r="A4948" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4948" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C4948" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="4949">
+      <c r="A4949" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4949" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C4949" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4950">
+      <c r="A4950" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4950" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4950" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="4951">
+      <c r="A4951" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4951" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C4951" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4952">
+      <c r="A4952" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4952" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C4952" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4953">
+      <c r="A4953" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4953" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C4953" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="4954">
+      <c r="A4954" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4954" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C4954" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="4955">
+      <c r="A4955" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4955" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4955" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="4956">
+      <c r="A4956" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4956" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C4956" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="4957">
+      <c r="A4957" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4957" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C4957" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4958">
+      <c r="A4958" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4958" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4958" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4959">
+      <c r="A4959" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B4959" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C4959" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4959"/>
+  <dimension ref="A1:C5025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74803,6 +74803,996 @@
         <v>13.2</v>
       </c>
     </row>
+    <row r="4960">
+      <c r="A4960" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4960" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C4960" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4961">
+      <c r="A4961" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4961" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C4961" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="4962">
+      <c r="A4962" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4962" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C4962" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="4963">
+      <c r="A4963" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4963" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C4963" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="4964">
+      <c r="A4964" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4964" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C4964" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="4965">
+      <c r="A4965" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4965" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C4965" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="4966">
+      <c r="A4966" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4966" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C4966" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4967">
+      <c r="A4967" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4967" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C4967" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="4968">
+      <c r="A4968" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4968" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C4968" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="4969">
+      <c r="A4969" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4969" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C4969" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="4970">
+      <c r="A4970" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4970" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C4970" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="4971">
+      <c r="A4971" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4971" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C4971" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="4972">
+      <c r="A4972" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4972" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4972" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="4973">
+      <c r="A4973" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4973" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C4973" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4974">
+      <c r="A4974" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4974" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C4974" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="4975">
+      <c r="A4975" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4975" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C4975" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="4976">
+      <c r="A4976" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4976" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C4976" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="4977">
+      <c r="A4977" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4977" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C4977" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="4978">
+      <c r="A4978" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4978" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C4978" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="4979">
+      <c r="A4979" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4979" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C4979" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="4980">
+      <c r="A4980" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4980" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C4980" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="4981">
+      <c r="A4981" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4981" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C4981" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4982">
+      <c r="A4982" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4982" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C4982" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4983">
+      <c r="A4983" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4983" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C4983" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4984">
+      <c r="A4984" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4984" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C4984" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="4985">
+      <c r="A4985" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4985" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C4985" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="4986">
+      <c r="A4986" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4986" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C4986" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="4987">
+      <c r="A4987" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4987" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C4987" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="4988">
+      <c r="A4988" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4988" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C4988" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="4989">
+      <c r="A4989" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4989" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C4989" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="4990">
+      <c r="A4990" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4990" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C4990" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="4991">
+      <c r="A4991" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4991" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C4991" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="4992">
+      <c r="A4992" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4992" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C4992" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="4993">
+      <c r="A4993" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4993" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C4993" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="4994">
+      <c r="A4994" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4994" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C4994" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4995">
+      <c r="A4995" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4995" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C4995" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="4996">
+      <c r="A4996" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4996" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C4996" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4997">
+      <c r="A4997" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4997" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C4997" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4998">
+      <c r="A4998" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4998" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C4998" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="4999">
+      <c r="A4999" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B4999" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C4999" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5000">
+      <c r="A5000" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5000" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5000" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5001">
+      <c r="A5001" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5001" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5001" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="5002">
+      <c r="A5002" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5002" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5002" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5003">
+      <c r="A5003" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5003" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5003" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="5004">
+      <c r="A5004" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5004" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5004" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5005">
+      <c r="A5005" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5005" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5005" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="5006">
+      <c r="A5006" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5006" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5006" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5007">
+      <c r="A5007" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5007" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5007" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="5008">
+      <c r="A5008" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5008" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5008" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5009">
+      <c r="A5009" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5009" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5009" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5010">
+      <c r="A5010" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5010" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5010" t="n">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="5011">
+      <c r="A5011" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5011" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5011" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5012">
+      <c r="A5012" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5012" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5012" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5013">
+      <c r="A5013" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5013" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5013" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5014">
+      <c r="A5014" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5014" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5014" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5015">
+      <c r="A5015" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5015" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5015" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="5016">
+      <c r="A5016" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5016" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5016" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="5017">
+      <c r="A5017" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5017" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5017" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5018">
+      <c r="A5018" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5018" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5018" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5019">
+      <c r="A5019" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5019" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5019" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="5020">
+      <c r="A5020" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5020" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5020" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5021">
+      <c r="A5021" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5021" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5021" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="5022">
+      <c r="A5022" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5022" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5022" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="5023">
+      <c r="A5023" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5023" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5023" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5024">
+      <c r="A5024" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5024" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5024" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="5025">
+      <c r="A5025" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B5025" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5025" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5025"/>
+  <dimension ref="A1:C5090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75793,6 +75793,981 @@
         <v>16.1</v>
       </c>
     </row>
+    <row r="5026">
+      <c r="A5026" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5026" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5026" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5027">
+      <c r="A5027" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5027" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5027" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5028">
+      <c r="A5028" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5028" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5028" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5029">
+      <c r="A5029" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5029" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5029" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5030">
+      <c r="A5030" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5030" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5030" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5031">
+      <c r="A5031" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5031" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5031" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5032">
+      <c r="A5032" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5032" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5032" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5033">
+      <c r="A5033" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5033" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5033" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="5034">
+      <c r="A5034" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5034" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5034" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5035">
+      <c r="A5035" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5035" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5035" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5036">
+      <c r="A5036" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5036" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5036" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="5037">
+      <c r="A5037" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5037" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5037" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5038">
+      <c r="A5038" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5038" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5038" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="5039">
+      <c r="A5039" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5039" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5039" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="5040">
+      <c r="A5040" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5040" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5040" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5041">
+      <c r="A5041" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5041" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5041" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="5042">
+      <c r="A5042" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5042" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5042" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5043">
+      <c r="A5043" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5043" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5043" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5044">
+      <c r="A5044" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5044" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5044" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5045">
+      <c r="A5045" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5045" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5045" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5046">
+      <c r="A5046" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5046" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5046" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="5047">
+      <c r="A5047" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5047" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5047" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5048">
+      <c r="A5048" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5048" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5048" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5049">
+      <c r="A5049" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5049" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5049" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5050">
+      <c r="A5050" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5050" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5050" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="5051">
+      <c r="A5051" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5051" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5051" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="5052">
+      <c r="A5052" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5052" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5052" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5053">
+      <c r="A5053" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5053" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5053" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5054">
+      <c r="A5054" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5054" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5054" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5055">
+      <c r="A5055" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5055" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5055" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5056">
+      <c r="A5056" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5056" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5056" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="5057">
+      <c r="A5057" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5057" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5057" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5058">
+      <c r="A5058" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5058" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5058" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5059">
+      <c r="A5059" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5059" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5059" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="5060">
+      <c r="A5060" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5060" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5060" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="5061">
+      <c r="A5061" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5061" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5061" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="5062">
+      <c r="A5062" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5062" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5062" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5063">
+      <c r="A5063" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5063" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5063" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="5064">
+      <c r="A5064" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5064" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5064" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5065">
+      <c r="A5065" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5065" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5065" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5066">
+      <c r="A5066" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5066" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5066" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="5067">
+      <c r="A5067" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5067" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5067" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="5068">
+      <c r="A5068" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5068" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5068" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="5069">
+      <c r="A5069" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5069" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5069" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5070">
+      <c r="A5070" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5070" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5070" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5071">
+      <c r="A5071" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5071" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5071" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5072">
+      <c r="A5072" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5072" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5072" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="5073">
+      <c r="A5073" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5073" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5073" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="5074">
+      <c r="A5074" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5074" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5074" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="5075">
+      <c r="A5075" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5075" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5075" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="5076">
+      <c r="A5076" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5076" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5076" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5077">
+      <c r="A5077" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5077" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5077" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5078">
+      <c r="A5078" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5078" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5078" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5079">
+      <c r="A5079" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5079" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5079" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5080">
+      <c r="A5080" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5080" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5080" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="5081">
+      <c r="A5081" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5081" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5081" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="5082">
+      <c r="A5082" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5082" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5082" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5083">
+      <c r="A5083" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5083" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5083" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="5084">
+      <c r="A5084" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5084" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5084" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="5085">
+      <c r="A5085" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5085" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5085" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="5086">
+      <c r="A5086" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5086" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5086" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="5087">
+      <c r="A5087" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5087" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5087" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5088">
+      <c r="A5088" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5088" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5088" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5089">
+      <c r="A5089" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5089" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5089" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="5090">
+      <c r="A5090" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B5090" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5090" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5090"/>
+  <dimension ref="A1:C5156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76768,6 +76768,996 @@
         <v>17.1</v>
       </c>
     </row>
+    <row r="5091">
+      <c r="A5091" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5091" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5091" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5092">
+      <c r="A5092" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5092" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5092" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5093">
+      <c r="A5093" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5093" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5093" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5094">
+      <c r="A5094" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5094" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5094" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5095">
+      <c r="A5095" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5095" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5095" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="5096">
+      <c r="A5096" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5096" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5096" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="5097">
+      <c r="A5097" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5097" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5097" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="5098">
+      <c r="A5098" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5098" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5098" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5099">
+      <c r="A5099" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5099" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5099" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5100">
+      <c r="A5100" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5100" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5100" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="5101">
+      <c r="A5101" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5101" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5101" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5102">
+      <c r="A5102" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5102" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5102" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5103">
+      <c r="A5103" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5103" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5103" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5104">
+      <c r="A5104" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5104" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5104" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="5105">
+      <c r="A5105" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5105" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5105" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="5106">
+      <c r="A5106" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5106" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5106" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="5107">
+      <c r="A5107" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5107" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5107" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5108">
+      <c r="A5108" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5108" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5108" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="5109">
+      <c r="A5109" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5109" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5109" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5110">
+      <c r="A5110" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5110" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5110" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5111">
+      <c r="A5111" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5111" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5111" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5112">
+      <c r="A5112" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5112" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5112" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="5113">
+      <c r="A5113" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5113" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5113" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5114">
+      <c r="A5114" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5114" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5114" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5115">
+      <c r="A5115" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5115" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5115" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="5116">
+      <c r="A5116" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5116" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5116" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="5117">
+      <c r="A5117" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5117" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5117" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="5118">
+      <c r="A5118" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5118" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5118" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="5119">
+      <c r="A5119" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5119" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5119" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5120">
+      <c r="A5120" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5120" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5120" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="5121">
+      <c r="A5121" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5121" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5121" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5122">
+      <c r="A5122" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5122" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5122" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="5123">
+      <c r="A5123" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5123" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5123" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5124">
+      <c r="A5124" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5124" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5124" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="5125">
+      <c r="A5125" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5125" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5125" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5126">
+      <c r="A5126" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5126" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5126" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5127">
+      <c r="A5127" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5127" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5127" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5128">
+      <c r="A5128" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5128" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5128" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="5129">
+      <c r="A5129" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5129" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5129" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5130">
+      <c r="A5130" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5130" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5130" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5131">
+      <c r="A5131" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5131" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5131" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5132">
+      <c r="A5132" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5132" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5132" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="5133">
+      <c r="A5133" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5133" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5133" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="5134">
+      <c r="A5134" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5134" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5134" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="5135">
+      <c r="A5135" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5135" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5135" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5136">
+      <c r="A5136" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5136" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5136" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5137">
+      <c r="A5137" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5137" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5137" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="5138">
+      <c r="A5138" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5138" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5138" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="5139">
+      <c r="A5139" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5139" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5139" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5140">
+      <c r="A5140" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5140" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5140" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5141">
+      <c r="A5141" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5141" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5141" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="5142">
+      <c r="A5142" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5142" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5142" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5143">
+      <c r="A5143" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5143" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5143" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5144">
+      <c r="A5144" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5144" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5144" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5145">
+      <c r="A5145" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5145" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5145" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="5146">
+      <c r="A5146" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5146" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5146" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="5147">
+      <c r="A5147" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5147" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5147" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5148">
+      <c r="A5148" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5148" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5148" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5149">
+      <c r="A5149" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5149" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5149" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="5150">
+      <c r="A5150" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5150" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5150" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="5151">
+      <c r="A5151" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5151" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5151" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5152">
+      <c r="A5152" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5152" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5152" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="5153">
+      <c r="A5153" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5153" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5153" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5154">
+      <c r="A5154" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5154" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5154" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5155">
+      <c r="A5155" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5155" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5155" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5156">
+      <c r="A5156" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5156" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5156" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5156"/>
+  <dimension ref="A1:C5220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77758,6 +77758,966 @@
         <v>13.8</v>
       </c>
     </row>
+    <row r="5157">
+      <c r="A5157" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5157" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5157" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5158">
+      <c r="A5158" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5158" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5158" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5159">
+      <c r="A5159" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5159" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5159" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5160">
+      <c r="A5160" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5160" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5160" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5161">
+      <c r="A5161" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5161" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5161" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="5162">
+      <c r="A5162" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5162" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5162" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="5163">
+      <c r="A5163" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5163" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5163" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="5164">
+      <c r="A5164" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5164" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5164" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5165">
+      <c r="A5165" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5165" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5165" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5166">
+      <c r="A5166" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5166" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5166" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5167">
+      <c r="A5167" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5167" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5167" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="5168">
+      <c r="A5168" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5168" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5168" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5169">
+      <c r="A5169" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5169" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5169" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5170">
+      <c r="A5170" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5170" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5170" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="5171">
+      <c r="A5171" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5171" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5171" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5172">
+      <c r="A5172" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5172" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5172" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5173">
+      <c r="A5173" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5173" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5173" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="5174">
+      <c r="A5174" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5174" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5174" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="5175">
+      <c r="A5175" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5175" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5175" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="5176">
+      <c r="A5176" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5176" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5176" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5177">
+      <c r="A5177" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5177" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5177" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="5178">
+      <c r="A5178" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5178" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5178" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5179">
+      <c r="A5179" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5179" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5179" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5180">
+      <c r="A5180" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5180" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5180" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="5181">
+      <c r="A5181" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5181" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5181" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="5182">
+      <c r="A5182" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5182" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5182" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5183">
+      <c r="A5183" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5183" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5183" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5184">
+      <c r="A5184" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5184" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5184" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5185">
+      <c r="A5185" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5185" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5185" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="5186">
+      <c r="A5186" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5186" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5186" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="5187">
+      <c r="A5187" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5187" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5187" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5188">
+      <c r="A5188" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5188" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5188" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="5189">
+      <c r="A5189" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5189" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5189" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="5190">
+      <c r="A5190" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5190" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5190" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="5191">
+      <c r="A5191" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5191" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5191" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5192">
+      <c r="A5192" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5192" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5192" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="5193">
+      <c r="A5193" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5193" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5193" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="5194">
+      <c r="A5194" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5194" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5194" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5195">
+      <c r="A5195" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5195" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5195" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5196">
+      <c r="A5196" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5196" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5196" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="5197">
+      <c r="A5197" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5197" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5197" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="5198">
+      <c r="A5198" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5198" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5198" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="5199">
+      <c r="A5199" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5199" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5199" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5200">
+      <c r="A5200" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5200" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5200" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5201">
+      <c r="A5201" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5201" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5201" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="5202">
+      <c r="A5202" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5202" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5202" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5203">
+      <c r="A5203" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5203" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5203" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="5204">
+      <c r="A5204" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5204" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5204" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5205">
+      <c r="A5205" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5205" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5205" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="5206">
+      <c r="A5206" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5206" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5206" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5207">
+      <c r="A5207" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5207" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5207" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="5208">
+      <c r="A5208" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5208" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5208" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5209">
+      <c r="A5209" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5209" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5209" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="5210">
+      <c r="A5210" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5210" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5210" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="5211">
+      <c r="A5211" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5211" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5211" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="5212">
+      <c r="A5212" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5212" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5212" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="5213">
+      <c r="A5213" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5213" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5213" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="5214">
+      <c r="A5214" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5214" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5214" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="5215">
+      <c r="A5215" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5215" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5215" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5216">
+      <c r="A5216" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5216" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5216" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5217">
+      <c r="A5217" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5217" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5217" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5218">
+      <c r="A5218" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5218" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5218" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="5219">
+      <c r="A5219" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5219" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5219" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5220">
+      <c r="A5220" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B5220" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5220" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5220"/>
+  <dimension ref="A1:C5287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78718,6 +78718,1011 @@
         <v>17.8</v>
       </c>
     </row>
+    <row r="5221">
+      <c r="A5221" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5221" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5221" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5222">
+      <c r="A5222" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5222" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5222" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="5223">
+      <c r="A5223" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5223" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5223" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="5224">
+      <c r="A5224" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5224" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5224" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="5225">
+      <c r="A5225" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5225" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5225" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="5226">
+      <c r="A5226" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5226" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5226" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5227">
+      <c r="A5227" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5227" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5227" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="5228">
+      <c r="A5228" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5228" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5228" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="5229">
+      <c r="A5229" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5229" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5229" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="5230">
+      <c r="A5230" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5230" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5230" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="5231">
+      <c r="A5231" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5231" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5231" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5232">
+      <c r="A5232" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5232" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5232" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="5233">
+      <c r="A5233" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5233" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5233" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5234">
+      <c r="A5234" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5234" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5234" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="5235">
+      <c r="A5235" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5235" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5235" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="5236">
+      <c r="A5236" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5236" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5236" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5237">
+      <c r="A5237" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5237" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5237" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="5238">
+      <c r="A5238" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5238" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5238" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="5239">
+      <c r="A5239" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5239" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5239" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="5240">
+      <c r="A5240" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5240" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5240" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="5241">
+      <c r="A5241" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5241" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5241" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="5242">
+      <c r="A5242" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5242" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5242" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5243">
+      <c r="A5243" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5243" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5243" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="5244">
+      <c r="A5244" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5244" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5244" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5245">
+      <c r="A5245" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5245" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5245" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5246">
+      <c r="A5246" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5246" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5246" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="5247">
+      <c r="A5247" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5247" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5247" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5248">
+      <c r="A5248" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5248" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5248" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5249">
+      <c r="A5249" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5249" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5249" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="5250">
+      <c r="A5250" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5250" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5250" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5251">
+      <c r="A5251" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5251" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5251" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="5252">
+      <c r="A5252" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5252" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5252" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="5253">
+      <c r="A5253" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5253" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5253" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="5254">
+      <c r="A5254" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5254" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5254" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5255">
+      <c r="A5255" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5255" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5255" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="5256">
+      <c r="A5256" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5256" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5256" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="5257">
+      <c r="A5257" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5257" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5257" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="5258">
+      <c r="A5258" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5258" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5258" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="5259">
+      <c r="A5259" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5259" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5259" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5260">
+      <c r="A5260" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5260" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5260" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="5261">
+      <c r="A5261" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5261" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5261" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="5262">
+      <c r="A5262" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5262" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5262" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="5263">
+      <c r="A5263" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5263" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5263" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="5264">
+      <c r="A5264" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5264" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5264" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="5265">
+      <c r="A5265" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5265" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5265" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="5266">
+      <c r="A5266" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5266" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5266" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="5267">
+      <c r="A5267" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5267" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5267" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="5268">
+      <c r="A5268" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5268" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5268" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5269">
+      <c r="A5269" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5269" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5269" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="5270">
+      <c r="A5270" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5270" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5270" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="5271">
+      <c r="A5271" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5271" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5271" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="5272">
+      <c r="A5272" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5272" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5272" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="5273">
+      <c r="A5273" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5273" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5273" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5274">
+      <c r="A5274" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5274" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5274" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5275">
+      <c r="A5275" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5275" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5275" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="5276">
+      <c r="A5276" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5276" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5276" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="5277">
+      <c r="A5277" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5277" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5277" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5278">
+      <c r="A5278" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5278" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5278" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="5279">
+      <c r="A5279" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5279" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5279" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="5280">
+      <c r="A5280" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5280" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5280" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="5281">
+      <c r="A5281" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5281" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5281" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="5282">
+      <c r="A5282" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5282" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5282" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5283">
+      <c r="A5283" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5283" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5283" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="5284">
+      <c r="A5284" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5284" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5284" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="5285">
+      <c r="A5285" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5285" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5285" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="5286">
+      <c r="A5286" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5286" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5286" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="5287">
+      <c r="A5287" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5287" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5287" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5287"/>
+  <dimension ref="A1:C5352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79723,6 +79723,981 @@
         <v>14.3</v>
       </c>
     </row>
+    <row r="5288">
+      <c r="A5288" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5288" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5288" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5289">
+      <c r="A5289" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5289" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5289" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="5290">
+      <c r="A5290" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5290" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5290" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="5291">
+      <c r="A5291" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5291" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5291" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5292">
+      <c r="A5292" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5292" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5292" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="5293">
+      <c r="A5293" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5293" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5293" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="5294">
+      <c r="A5294" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5294" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5294" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="5295">
+      <c r="A5295" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5295" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5295" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="5296">
+      <c r="A5296" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5296" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5296" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5297">
+      <c r="A5297" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5297" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5297" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="5298">
+      <c r="A5298" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5298" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5298" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5299">
+      <c r="A5299" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5299" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5299" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5300">
+      <c r="A5300" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5300" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5300" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5301">
+      <c r="A5301" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5301" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5301" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5302">
+      <c r="A5302" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5302" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5302" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5303">
+      <c r="A5303" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5303" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5303" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="5304">
+      <c r="A5304" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5304" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5304" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5305">
+      <c r="A5305" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5305" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5305" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5306">
+      <c r="A5306" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5306" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5306" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="5307">
+      <c r="A5307" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5307" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5307" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="5308">
+      <c r="A5308" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5308" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5308" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5309">
+      <c r="A5309" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5309" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5309" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5310">
+      <c r="A5310" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5310" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5310" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5311">
+      <c r="A5311" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5311" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5311" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="5312">
+      <c r="A5312" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5312" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5312" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5313">
+      <c r="A5313" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5313" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5313" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="5314">
+      <c r="A5314" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5314" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5314" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5315">
+      <c r="A5315" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5315" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5315" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="5316">
+      <c r="A5316" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5316" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5316" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="5317">
+      <c r="A5317" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5317" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5317" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5318">
+      <c r="A5318" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5318" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5318" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="5319">
+      <c r="A5319" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5319" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5319" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5320">
+      <c r="A5320" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5320" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5320" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="5321">
+      <c r="A5321" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5321" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5321" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="5322">
+      <c r="A5322" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5322" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5322" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="5323">
+      <c r="A5323" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5323" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5323" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5324">
+      <c r="A5324" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5324" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5324" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5325">
+      <c r="A5325" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5325" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5325" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5326">
+      <c r="A5326" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5326" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5326" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5327">
+      <c r="A5327" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5327" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5327" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="5328">
+      <c r="A5328" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5328" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5328" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5329">
+      <c r="A5329" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5329" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5329" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5330">
+      <c r="A5330" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5330" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5330" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="5331">
+      <c r="A5331" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5331" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5331" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5332">
+      <c r="A5332" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5332" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5332" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="5333">
+      <c r="A5333" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5333" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5333" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5334">
+      <c r="A5334" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5334" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5334" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5335">
+      <c r="A5335" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5335" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5335" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5336">
+      <c r="A5336" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5336" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5336" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5337">
+      <c r="A5337" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5337" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5337" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5338">
+      <c r="A5338" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5338" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5338" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5339">
+      <c r="A5339" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5339" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5339" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="5340">
+      <c r="A5340" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5340" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5340" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="5341">
+      <c r="A5341" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5341" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5341" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="5342">
+      <c r="A5342" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5342" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5342" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="5343">
+      <c r="A5343" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5343" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5343" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5344">
+      <c r="A5344" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5344" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5344" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="5345">
+      <c r="A5345" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5345" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5345" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5346">
+      <c r="A5346" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5346" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5346" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5347">
+      <c r="A5347" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5347" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5347" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="5348">
+      <c r="A5348" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5348" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5348" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="5349">
+      <c r="A5349" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5349" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5349" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="5350">
+      <c r="A5350" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5350" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5350" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5351">
+      <c r="A5351" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5351" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5351" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="5352">
+      <c r="A5352" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B5352" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5352" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5352"/>
+  <dimension ref="A1:C5416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80698,6 +80698,966 @@
         <v>14.3</v>
       </c>
     </row>
+    <row r="5353">
+      <c r="A5353" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5353" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5353" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5354">
+      <c r="A5354" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5354" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5354" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5355">
+      <c r="A5355" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5355" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5355" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5356">
+      <c r="A5356" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5356" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5356" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5357">
+      <c r="A5357" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5357" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5357" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5358">
+      <c r="A5358" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5358" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5358" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="5359">
+      <c r="A5359" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5359" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5359" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="5360">
+      <c r="A5360" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5360" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5360" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="5361">
+      <c r="A5361" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5361" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5361" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5362">
+      <c r="A5362" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5362" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5362" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5363">
+      <c r="A5363" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5363" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5363" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5364">
+      <c r="A5364" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5364" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5364" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5365">
+      <c r="A5365" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5365" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5365" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="5366">
+      <c r="A5366" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5366" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5366" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="5367">
+      <c r="A5367" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5367" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5367" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5368">
+      <c r="A5368" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5368" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5368" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5369">
+      <c r="A5369" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5369" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5369" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5370">
+      <c r="A5370" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5370" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5370" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="5371">
+      <c r="A5371" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5371" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5371" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5372">
+      <c r="A5372" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5372" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5372" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="5373">
+      <c r="A5373" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5373" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5373" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5374">
+      <c r="A5374" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5374" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5374" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="5375">
+      <c r="A5375" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5375" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5375" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5376">
+      <c r="A5376" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5376" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5376" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5377">
+      <c r="A5377" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5377" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5377" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="5378">
+      <c r="A5378" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5378" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5378" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5379">
+      <c r="A5379" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5379" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5379" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5380">
+      <c r="A5380" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5380" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5380" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5381">
+      <c r="A5381" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5381" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5381" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="5382">
+      <c r="A5382" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5382" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5382" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="5383">
+      <c r="A5383" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5383" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5383" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="5384">
+      <c r="A5384" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5384" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5384" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="5385">
+      <c r="A5385" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5385" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5385" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5386">
+      <c r="A5386" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5386" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5386" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="5387">
+      <c r="A5387" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5387" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5387" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="5388">
+      <c r="A5388" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5388" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5388" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5389">
+      <c r="A5389" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5389" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5389" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="5390">
+      <c r="A5390" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5390" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5390" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="5391">
+      <c r="A5391" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5391" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5391" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5392">
+      <c r="A5392" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5392" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5392" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5393">
+      <c r="A5393" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5393" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5393" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="5394">
+      <c r="A5394" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5394" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5394" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="5395">
+      <c r="A5395" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5395" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5395" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="5396">
+      <c r="A5396" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5396" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5396" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="5397">
+      <c r="A5397" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5397" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5397" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="5398">
+      <c r="A5398" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5398" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5398" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5399">
+      <c r="A5399" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5399" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5399" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="5400">
+      <c r="A5400" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5400" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5400" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5401">
+      <c r="A5401" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5401" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5401" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="5402">
+      <c r="A5402" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5402" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5402" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5403">
+      <c r="A5403" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5403" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5403" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="5404">
+      <c r="A5404" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5404" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5404" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5405">
+      <c r="A5405" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5405" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5405" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="5406">
+      <c r="A5406" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5406" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5406" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5407">
+      <c r="A5407" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5407" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5407" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5408">
+      <c r="A5408" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5408" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5408" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5409">
+      <c r="A5409" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5409" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5409" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5410">
+      <c r="A5410" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5410" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5410" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5411">
+      <c r="A5411" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5411" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5411" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="5412">
+      <c r="A5412" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5412" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5412" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="5413">
+      <c r="A5413" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5413" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5413" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="5414">
+      <c r="A5414" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5414" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5414" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="5415">
+      <c r="A5415" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5415" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5415" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="5416">
+      <c r="A5416" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B5416" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5416" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5416"/>
+  <dimension ref="A1:C5483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81658,6 +81658,1011 @@
         <v>15.6</v>
       </c>
     </row>
+    <row r="5417">
+      <c r="A5417" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5417" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5417" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5418">
+      <c r="A5418" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5418" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5418" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5419">
+      <c r="A5419" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5419" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5419" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5420">
+      <c r="A5420" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5420" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5420" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5421">
+      <c r="A5421" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5421" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5421" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="5422">
+      <c r="A5422" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5422" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5422" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5423">
+      <c r="A5423" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5423" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5423" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5424">
+      <c r="A5424" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5424" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5424" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="5425">
+      <c r="A5425" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5425" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5425" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="5426">
+      <c r="A5426" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5426" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5426" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="5427">
+      <c r="A5427" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5427" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5427" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="5428">
+      <c r="A5428" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5428" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5428" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="5429">
+      <c r="A5429" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5429" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5429" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="5430">
+      <c r="A5430" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5430" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5430" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="5431">
+      <c r="A5431" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5431" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5431" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5432">
+      <c r="A5432" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5432" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5432" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="5433">
+      <c r="A5433" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5433" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5433" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="5434">
+      <c r="A5434" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5434" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5434" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="5435">
+      <c r="A5435" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5435" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5435" t="n">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="5436">
+      <c r="A5436" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5436" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5436" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="5437">
+      <c r="A5437" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5437" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5437" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="5438">
+      <c r="A5438" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5438" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5438" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="5439">
+      <c r="A5439" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5439" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5439" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="5440">
+      <c r="A5440" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5440" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5440" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5441">
+      <c r="A5441" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5441" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5441" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5442">
+      <c r="A5442" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5442" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5442" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5443">
+      <c r="A5443" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5443" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5443" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="5444">
+      <c r="A5444" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5444" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5444" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="5445">
+      <c r="A5445" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5445" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5445" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="5446">
+      <c r="A5446" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5446" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5446" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="5447">
+      <c r="A5447" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5447" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5447" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="5448">
+      <c r="A5448" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5448" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5448" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5449">
+      <c r="A5449" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5449" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5449" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="5450">
+      <c r="A5450" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5450" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5450" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="5451">
+      <c r="A5451" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5451" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5451" t="n">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="5452">
+      <c r="A5452" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5452" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5452" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5453">
+      <c r="A5453" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5453" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5453" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5454">
+      <c r="A5454" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5454" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5454" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="5455">
+      <c r="A5455" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5455" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5455" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5456">
+      <c r="A5456" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5456" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5456" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="5457">
+      <c r="A5457" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5457" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5457" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5458">
+      <c r="A5458" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5458" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5458" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5459">
+      <c r="A5459" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5459" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5459" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5460">
+      <c r="A5460" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5460" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5460" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="5461">
+      <c r="A5461" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5461" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5461" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="5462">
+      <c r="A5462" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5462" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5462" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="5463">
+      <c r="A5463" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5463" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5463" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5464">
+      <c r="A5464" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5464" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5464" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5465">
+      <c r="A5465" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5465" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5465" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="5466">
+      <c r="A5466" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5466" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5466" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5467">
+      <c r="A5467" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5467" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5467" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5468">
+      <c r="A5468" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5468" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5468" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5469">
+      <c r="A5469" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5469" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5469" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="5470">
+      <c r="A5470" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5470" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5470" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5471">
+      <c r="A5471" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5471" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5471" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5472">
+      <c r="A5472" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5472" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5472" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="5473">
+      <c r="A5473" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5473" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5473" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5474">
+      <c r="A5474" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5474" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5474" t="n">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="5475">
+      <c r="A5475" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5475" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5475" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="5476">
+      <c r="A5476" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5476" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5476" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5477">
+      <c r="A5477" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5477" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5477" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5478">
+      <c r="A5478" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5478" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5478" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="5479">
+      <c r="A5479" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5479" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5479" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5480">
+      <c r="A5480" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5480" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5480" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="5481">
+      <c r="A5481" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5481" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5481" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="5482">
+      <c r="A5482" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5482" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5482" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5483">
+      <c r="A5483" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5483" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5483" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5483"/>
+  <dimension ref="A1:C5550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82663,6 +82663,1011 @@
         <v>18.2</v>
       </c>
     </row>
+    <row r="5484">
+      <c r="A5484" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5484" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5484" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5485">
+      <c r="A5485" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5485" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5485" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="5486">
+      <c r="A5486" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5486" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5486" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="5487">
+      <c r="A5487" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5487" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5487" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="5488">
+      <c r="A5488" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5488" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5488" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="5489">
+      <c r="A5489" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5489" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5489" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5490">
+      <c r="A5490" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5490" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5490" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5491">
+      <c r="A5491" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5491" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5491" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="5492">
+      <c r="A5492" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5492" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5492" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5493">
+      <c r="A5493" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5493" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5493" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="5494">
+      <c r="A5494" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5494" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5494" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="5495">
+      <c r="A5495" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5495" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5495" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="5496">
+      <c r="A5496" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5496" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5496" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5497">
+      <c r="A5497" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5497" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5497" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5498">
+      <c r="A5498" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5498" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5498" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="5499">
+      <c r="A5499" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5499" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5499" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="5500">
+      <c r="A5500" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5500" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5500" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5501">
+      <c r="A5501" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5501" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5501" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5502">
+      <c r="A5502" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5502" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5502" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="5503">
+      <c r="A5503" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5503" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5503" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5504">
+      <c r="A5504" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5504" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5504" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="5505">
+      <c r="A5505" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5505" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5505" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="5506">
+      <c r="A5506" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5506" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5506" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="5507">
+      <c r="A5507" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5507" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5507" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="5508">
+      <c r="A5508" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5508" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5508" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5509">
+      <c r="A5509" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5509" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5509" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5510">
+      <c r="A5510" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5510" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5510" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5511">
+      <c r="A5511" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5511" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5511" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="5512">
+      <c r="A5512" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5512" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5512" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="5513">
+      <c r="A5513" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5513" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5513" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="5514">
+      <c r="A5514" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5514" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5514" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="5515">
+      <c r="A5515" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5515" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5515" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5516">
+      <c r="A5516" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5516" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5516" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="5517">
+      <c r="A5517" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5517" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5517" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5518">
+      <c r="A5518" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5518" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5518" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="5519">
+      <c r="A5519" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5519" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5519" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5520">
+      <c r="A5520" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5520" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5520" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="5521">
+      <c r="A5521" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5521" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5521" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5522">
+      <c r="A5522" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5522" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5522" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5523">
+      <c r="A5523" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5523" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5523" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5524">
+      <c r="A5524" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5524" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5524" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5525">
+      <c r="A5525" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5525" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5525" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5526">
+      <c r="A5526" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5526" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5526" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5527">
+      <c r="A5527" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5527" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5527" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5528">
+      <c r="A5528" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5528" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5528" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="5529">
+      <c r="A5529" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5529" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5529" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="5530">
+      <c r="A5530" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5530" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5530" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5531">
+      <c r="A5531" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5531" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5531" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5532">
+      <c r="A5532" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5532" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5532" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="5533">
+      <c r="A5533" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5533" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5533" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="5534">
+      <c r="A5534" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5534" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5534" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5535">
+      <c r="A5535" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5535" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5535" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="5536">
+      <c r="A5536" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5536" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5536" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5537">
+      <c r="A5537" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5537" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5537" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="5538">
+      <c r="A5538" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5538" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5538" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5539">
+      <c r="A5539" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5539" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5539" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="5540">
+      <c r="A5540" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5540" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5540" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="5541">
+      <c r="A5541" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5541" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5541" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="5542">
+      <c r="A5542" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5542" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5542" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5543">
+      <c r="A5543" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5543" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5543" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5544">
+      <c r="A5544" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5544" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5544" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5545">
+      <c r="A5545" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5545" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5545" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="5546">
+      <c r="A5546" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5546" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5546" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5547">
+      <c r="A5547" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5547" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5547" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5548">
+      <c r="A5548" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5548" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5548" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5549">
+      <c r="A5549" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5549" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5549" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5550">
+      <c r="A5550" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5550" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5550" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5550"/>
+  <dimension ref="A1:C5617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83668,6 +83668,1011 @@
         <v>11.8</v>
       </c>
     </row>
+    <row r="5551">
+      <c r="A5551" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5551" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5551" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5552">
+      <c r="A5552" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5552" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5552" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="5553">
+      <c r="A5553" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5553" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5553" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="5554">
+      <c r="A5554" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5554" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5554" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="5555">
+      <c r="A5555" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5555" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5555" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="5556">
+      <c r="A5556" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5556" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5556" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="5557">
+      <c r="A5557" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5557" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5557" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="5558">
+      <c r="A5558" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5558" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5558" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="5559">
+      <c r="A5559" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5559" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5559" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="5560">
+      <c r="A5560" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5560" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5560" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="5561">
+      <c r="A5561" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5561" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5561" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="5562">
+      <c r="A5562" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5562" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5562" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5563">
+      <c r="A5563" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5563" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5563" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5564">
+      <c r="A5564" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5564" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5564" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="5565">
+      <c r="A5565" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5565" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5565" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="5566">
+      <c r="A5566" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5566" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5566" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="5567">
+      <c r="A5567" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5567" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5567" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="5568">
+      <c r="A5568" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5568" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5568" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="5569">
+      <c r="A5569" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5569" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5569" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5570">
+      <c r="A5570" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5570" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5570" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="5571">
+      <c r="A5571" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5571" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5571" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5572">
+      <c r="A5572" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5572" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5572" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="5573">
+      <c r="A5573" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5573" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5573" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="5574">
+      <c r="A5574" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5574" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5574" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="5575">
+      <c r="A5575" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5575" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5575" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5576">
+      <c r="A5576" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5576" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5576" t="n">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="5577">
+      <c r="A5577" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5577" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5577" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5578">
+      <c r="A5578" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5578" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5578" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5579">
+      <c r="A5579" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5579" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5579" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5580">
+      <c r="A5580" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5580" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5580" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="5581">
+      <c r="A5581" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5581" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5581" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5582">
+      <c r="A5582" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5582" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5582" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="5583">
+      <c r="A5583" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5583" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5583" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="5584">
+      <c r="A5584" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5584" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5584" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="5585">
+      <c r="A5585" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5585" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5585" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="5586">
+      <c r="A5586" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5586" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5586" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="5587">
+      <c r="A5587" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5587" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5587" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5588">
+      <c r="A5588" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5588" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5588" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="5589">
+      <c r="A5589" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5589" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5589" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5590">
+      <c r="A5590" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5590" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5590" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5591">
+      <c r="A5591" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5591" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5591" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5592">
+      <c r="A5592" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5592" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5592" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="5593">
+      <c r="A5593" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5593" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5593" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5594">
+      <c r="A5594" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5594" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5594" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5595">
+      <c r="A5595" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5595" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5595" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="5596">
+      <c r="A5596" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5596" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5596" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="5597">
+      <c r="A5597" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5597" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5597" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="5598">
+      <c r="A5598" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5598" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5598" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="5599">
+      <c r="A5599" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5599" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5599" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5600">
+      <c r="A5600" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5600" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5600" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="5601">
+      <c r="A5601" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5601" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5601" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5602">
+      <c r="A5602" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5602" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5602" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="5603">
+      <c r="A5603" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5603" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5603" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="5604">
+      <c r="A5604" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5604" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5604" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="5605">
+      <c r="A5605" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5605" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5605" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5606">
+      <c r="A5606" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5606" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5606" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="5607">
+      <c r="A5607" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5607" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5607" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5608">
+      <c r="A5608" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5608" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5608" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="5609">
+      <c r="A5609" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5609" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5609" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="5610">
+      <c r="A5610" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5610" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5610" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="5611">
+      <c r="A5611" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5611" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5611" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5612">
+      <c r="A5612" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5612" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5612" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5613">
+      <c r="A5613" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5613" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5613" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5614">
+      <c r="A5614" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5614" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5614" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="5615">
+      <c r="A5615" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5615" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5615" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5616">
+      <c r="A5616" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5616" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5616" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="5617">
+      <c r="A5617" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B5617" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5617" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5617"/>
+  <dimension ref="A1:C5683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84673,6 +84673,996 @@
         <v>10.2</v>
       </c>
     </row>
+    <row r="5618">
+      <c r="A5618" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5618" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5618" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5619">
+      <c r="A5619" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5619" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5619" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="5620">
+      <c r="A5620" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5620" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5620" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="5621">
+      <c r="A5621" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5621" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5621" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5622">
+      <c r="A5622" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5622" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5622" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="5623">
+      <c r="A5623" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5623" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5623" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5624">
+      <c r="A5624" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5624" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5624" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5625">
+      <c r="A5625" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5625" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5625" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5626">
+      <c r="A5626" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5626" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5626" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="5627">
+      <c r="A5627" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5627" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5627" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5628">
+      <c r="A5628" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5628" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5628" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5629">
+      <c r="A5629" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5629" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5629" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5630">
+      <c r="A5630" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5630" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5630" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="5631">
+      <c r="A5631" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5631" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5631" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5632">
+      <c r="A5632" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5632" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5632" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="5633">
+      <c r="A5633" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5633" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5633" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="5634">
+      <c r="A5634" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5634" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5634" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="5635">
+      <c r="A5635" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5635" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5635" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5636">
+      <c r="A5636" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5636" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5636" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5637">
+      <c r="A5637" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5637" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5637" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="5638">
+      <c r="A5638" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5638" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5638" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="5639">
+      <c r="A5639" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5639" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5639" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="5640">
+      <c r="A5640" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5640" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5640" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="5641">
+      <c r="A5641" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5641" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5641" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="5642">
+      <c r="A5642" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5642" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5642" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5643">
+      <c r="A5643" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5643" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5643" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5644">
+      <c r="A5644" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5644" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5644" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5645">
+      <c r="A5645" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5645" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5645" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="5646">
+      <c r="A5646" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5646" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5646" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5647">
+      <c r="A5647" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5647" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5647" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="5648">
+      <c r="A5648" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5648" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5648" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5649">
+      <c r="A5649" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5649" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5649" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="5650">
+      <c r="A5650" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5650" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5650" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5651">
+      <c r="A5651" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5651" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5651" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="5652">
+      <c r="A5652" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5652" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5652" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5653">
+      <c r="A5653" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5653" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5653" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="5654">
+      <c r="A5654" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5654" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5654" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5655">
+      <c r="A5655" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5655" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5655" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5656">
+      <c r="A5656" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5656" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5656" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="5657">
+      <c r="A5657" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5657" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5657" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="5658">
+      <c r="A5658" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5658" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5658" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5659">
+      <c r="A5659" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5659" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5659" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5660">
+      <c r="A5660" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5660" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5660" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="5661">
+      <c r="A5661" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5661" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5661" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5662">
+      <c r="A5662" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5662" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5662" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5663">
+      <c r="A5663" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5663" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5663" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="5664">
+      <c r="A5664" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5664" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5664" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5665">
+      <c r="A5665" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5665" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5665" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="5666">
+      <c r="A5666" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5666" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5666" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5667">
+      <c r="A5667" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5667" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5667" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5668">
+      <c r="A5668" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5668" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5668" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="5669">
+      <c r="A5669" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5669" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5669" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5670">
+      <c r="A5670" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5670" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5670" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="5671">
+      <c r="A5671" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5671" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5671" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5672">
+      <c r="A5672" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5672" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5672" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="5673">
+      <c r="A5673" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5673" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5673" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="5674">
+      <c r="A5674" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5674" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5674" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5675">
+      <c r="A5675" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5675" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5675" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="5676">
+      <c r="A5676" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5676" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5676" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5677">
+      <c r="A5677" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5677" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5677" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="5678">
+      <c r="A5678" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5678" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5678" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="5679">
+      <c r="A5679" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5679" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5679" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="5680">
+      <c r="A5680" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5680" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5680" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5681">
+      <c r="A5681" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5681" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5681" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="5682">
+      <c r="A5682" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5682" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5682" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="5683">
+      <c r="A5683" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B5683" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5683" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5683"/>
+  <dimension ref="A1:C5749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85663,6 +85663,996 @@
         <v>10.3</v>
       </c>
     </row>
+    <row r="5684">
+      <c r="A5684" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5684" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5684" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5685">
+      <c r="A5685" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5685" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5685" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="5686">
+      <c r="A5686" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5686" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5686" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5687">
+      <c r="A5687" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5687" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5687" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="5688">
+      <c r="A5688" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5688" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5688" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="5689">
+      <c r="A5689" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5689" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5689" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5690">
+      <c r="A5690" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5690" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5690" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5691">
+      <c r="A5691" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5691" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5691" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="5692">
+      <c r="A5692" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5692" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5692" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="5693">
+      <c r="A5693" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5693" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5693" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="5694">
+      <c r="A5694" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5694" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5694" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5695">
+      <c r="A5695" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5695" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5695" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="5696">
+      <c r="A5696" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5696" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5696" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5697">
+      <c r="A5697" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5697" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5697" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="5698">
+      <c r="A5698" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5698" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5698" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="5699">
+      <c r="A5699" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5699" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5699" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5700">
+      <c r="A5700" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5700" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5700" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5701">
+      <c r="A5701" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5701" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5701" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5702">
+      <c r="A5702" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5702" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5702" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5703">
+      <c r="A5703" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5703" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5703" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5704">
+      <c r="A5704" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5704" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5704" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5705">
+      <c r="A5705" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5705" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5705" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="5706">
+      <c r="A5706" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5706" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5706" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="5707">
+      <c r="A5707" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5707" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5707" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5708">
+      <c r="A5708" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5708" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5708" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="5709">
+      <c r="A5709" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5709" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5709" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="5710">
+      <c r="A5710" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5710" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5710" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5711">
+      <c r="A5711" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5711" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5711" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="5712">
+      <c r="A5712" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5712" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5712" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="5713">
+      <c r="A5713" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5713" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5713" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5714">
+      <c r="A5714" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5714" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5714" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5715">
+      <c r="A5715" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5715" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5715" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5716">
+      <c r="A5716" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5716" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5716" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5717">
+      <c r="A5717" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5717" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5717" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="5718">
+      <c r="A5718" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5718" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5718" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5719">
+      <c r="A5719" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5719" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5719" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="5720">
+      <c r="A5720" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5720" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5720" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="5721">
+      <c r="A5721" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5721" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5721" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5722">
+      <c r="A5722" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5722" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5722" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="5723">
+      <c r="A5723" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5723" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5723" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5724">
+      <c r="A5724" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5724" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5724" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5725">
+      <c r="A5725" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5725" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5725" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="5726">
+      <c r="A5726" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5726" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5726" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="5727">
+      <c r="A5727" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5727" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5727" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="5728">
+      <c r="A5728" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5728" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5728" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5729">
+      <c r="A5729" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5729" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5729" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5730">
+      <c r="A5730" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5730" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5730" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5731">
+      <c r="A5731" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5731" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5731" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="5732">
+      <c r="A5732" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5732" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5732" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5733">
+      <c r="A5733" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5733" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5733" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="5734">
+      <c r="A5734" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5734" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5734" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5735">
+      <c r="A5735" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5735" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5735" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5736">
+      <c r="A5736" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5736" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5736" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="5737">
+      <c r="A5737" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5737" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5737" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5738">
+      <c r="A5738" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5738" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5738" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5739">
+      <c r="A5739" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5739" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5739" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="5740">
+      <c r="A5740" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5740" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5740" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5741">
+      <c r="A5741" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5741" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5741" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="5742">
+      <c r="A5742" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5742" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5742" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5743">
+      <c r="A5743" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5743" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5743" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="5744">
+      <c r="A5744" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5744" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5744" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5745">
+      <c r="A5745" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5745" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5745" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="5746">
+      <c r="A5746" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5746" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5746" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="5747">
+      <c r="A5747" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5747" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5747" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5748">
+      <c r="A5748" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5748" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5748" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="5749">
+      <c r="A5749" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B5749" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5749" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5749"/>
+  <dimension ref="A1:C5814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86653,6 +86653,981 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5750">
+      <c r="A5750" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5750" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5750" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5751">
+      <c r="A5751" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5751" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5751" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="5752">
+      <c r="A5752" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5752" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5752" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5753">
+      <c r="A5753" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5753" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5753" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5754">
+      <c r="A5754" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5754" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5754" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="5755">
+      <c r="A5755" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5755" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5755" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5756">
+      <c r="A5756" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5756" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5756" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="5757">
+      <c r="A5757" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5757" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5757" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="5758">
+      <c r="A5758" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5758" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5758" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5759">
+      <c r="A5759" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5759" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5759" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5760">
+      <c r="A5760" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5760" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5760" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="5761">
+      <c r="A5761" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5761" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5761" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5762">
+      <c r="A5762" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5762" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5762" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="5763">
+      <c r="A5763" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5763" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5763" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="5764">
+      <c r="A5764" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5764" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5764" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="5765">
+      <c r="A5765" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5765" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5765" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="5766">
+      <c r="A5766" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5766" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5766" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="5767">
+      <c r="A5767" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5767" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5767" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="5768">
+      <c r="A5768" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5768" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5768" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="5769">
+      <c r="A5769" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5769" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5769" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="5770">
+      <c r="A5770" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5770" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5770" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5771">
+      <c r="A5771" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5771" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5771" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="5772">
+      <c r="A5772" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5772" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5772" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5773">
+      <c r="A5773" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5773" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5773" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="5774">
+      <c r="A5774" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5774" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5774" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5775">
+      <c r="A5775" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5775" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5775" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="5776">
+      <c r="A5776" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5776" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5776" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5777">
+      <c r="A5777" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5777" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5777" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="5778">
+      <c r="A5778" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5778" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5778" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="5779">
+      <c r="A5779" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5779" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5779" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5780">
+      <c r="A5780" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5780" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5780" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5781">
+      <c r="A5781" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5781" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5781" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="5782">
+      <c r="A5782" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5782" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5782" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="5783">
+      <c r="A5783" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5783" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5783" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="5784">
+      <c r="A5784" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5784" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5784" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="5785">
+      <c r="A5785" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5785" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5785" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="5786">
+      <c r="A5786" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5786" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5786" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="5787">
+      <c r="A5787" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5787" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5787" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="5788">
+      <c r="A5788" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5788" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5788" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5789">
+      <c r="A5789" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5789" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5789" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5790">
+      <c r="A5790" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5790" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5790" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="5791">
+      <c r="A5791" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5791" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5791" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5792">
+      <c r="A5792" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5792" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5792" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5793">
+      <c r="A5793" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5793" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5793" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="5794">
+      <c r="A5794" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5794" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5794" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="5795">
+      <c r="A5795" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5795" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5795" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="5796">
+      <c r="A5796" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5796" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5796" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="5797">
+      <c r="A5797" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5797" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5797" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5798">
+      <c r="A5798" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5798" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5798" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="5799">
+      <c r="A5799" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5799" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5799" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="5800">
+      <c r="A5800" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5800" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5800" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5801">
+      <c r="A5801" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5801" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5801" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5802">
+      <c r="A5802" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5802" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5802" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="5803">
+      <c r="A5803" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5803" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5803" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="5804">
+      <c r="A5804" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5804" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5804" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5805">
+      <c r="A5805" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5805" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5805" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="5806">
+      <c r="A5806" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5806" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5806" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5807">
+      <c r="A5807" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5807" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5807" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5808">
+      <c r="A5808" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5808" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5808" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="5809">
+      <c r="A5809" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5809" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5809" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5810">
+      <c r="A5810" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5810" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5810" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="5811">
+      <c r="A5811" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5811" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5811" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="5812">
+      <c r="A5812" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5812" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5812" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5813">
+      <c r="A5813" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5813" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5813" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="5814">
+      <c r="A5814" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5814" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5814" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5814"/>
+  <dimension ref="A1:C5880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87628,6 +87628,996 @@
         <v>6.9</v>
       </c>
     </row>
+    <row r="5815">
+      <c r="A5815" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5815" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5815" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5816">
+      <c r="A5816" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5816" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5816" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5817">
+      <c r="A5817" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5817" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5817" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5818">
+      <c r="A5818" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5818" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5818" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5819">
+      <c r="A5819" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5819" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5819" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="5820">
+      <c r="A5820" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5820" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5820" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="5821">
+      <c r="A5821" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5821" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5821" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5822">
+      <c r="A5822" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5822" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5822" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="5823">
+      <c r="A5823" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5823" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5823" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5824">
+      <c r="A5824" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5824" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5824" t="n">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="5825">
+      <c r="A5825" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5825" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5825" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5826">
+      <c r="A5826" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5826" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5826" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5827">
+      <c r="A5827" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5827" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5827" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5828">
+      <c r="A5828" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5828" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5828" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5829">
+      <c r="A5829" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5829" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5829" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="5830">
+      <c r="A5830" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5830" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5830" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="5831">
+      <c r="A5831" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5831" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5831" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5832">
+      <c r="A5832" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5832" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5832" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5833">
+      <c r="A5833" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5833" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5833" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5834">
+      <c r="A5834" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5834" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5834" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="5835">
+      <c r="A5835" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5835" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5835" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5836">
+      <c r="A5836" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5836" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5836" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="5837">
+      <c r="A5837" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5837" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5837" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="5838">
+      <c r="A5838" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5838" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5838" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5839">
+      <c r="A5839" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5839" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5839" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5840">
+      <c r="A5840" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5840" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5840" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="5841">
+      <c r="A5841" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5841" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5841" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5842">
+      <c r="A5842" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5842" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5842" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="5843">
+      <c r="A5843" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5843" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5843" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="5844">
+      <c r="A5844" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5844" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5844" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="5845">
+      <c r="A5845" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5845" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5845" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5846">
+      <c r="A5846" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5846" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5846" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="5847">
+      <c r="A5847" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5847" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5847" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5848">
+      <c r="A5848" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5848" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5848" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5849">
+      <c r="A5849" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5849" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5849" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="5850">
+      <c r="A5850" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5850" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5850" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="5851">
+      <c r="A5851" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5851" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5851" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="5852">
+      <c r="A5852" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5852" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5852" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5853">
+      <c r="A5853" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5853" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5853" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="5854">
+      <c r="A5854" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5854" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5854" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="5855">
+      <c r="A5855" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5855" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5855" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5856">
+      <c r="A5856" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5856" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5856" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5857">
+      <c r="A5857" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5857" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5857" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5858">
+      <c r="A5858" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5858" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5858" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="5859">
+      <c r="A5859" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5859" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5859" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="5860">
+      <c r="A5860" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5860" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5860" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5861">
+      <c r="A5861" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5861" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5861" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="5862">
+      <c r="A5862" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5862" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5862" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5863">
+      <c r="A5863" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5863" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5863" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="5864">
+      <c r="A5864" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5864" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5864" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="5865">
+      <c r="A5865" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5865" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5865" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5866">
+      <c r="A5866" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5866" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5866" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5867">
+      <c r="A5867" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5867" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5867" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5868">
+      <c r="A5868" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5868" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5868" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5869">
+      <c r="A5869" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5869" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5869" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5870">
+      <c r="A5870" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5870" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5870" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5871">
+      <c r="A5871" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5871" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5871" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5872">
+      <c r="A5872" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5872" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5872" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="5873">
+      <c r="A5873" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5873" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5873" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5874">
+      <c r="A5874" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5874" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5874" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="5875">
+      <c r="A5875" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5875" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5875" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="5876">
+      <c r="A5876" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5876" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5876" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="5877">
+      <c r="A5877" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5877" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5877" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="5878">
+      <c r="A5878" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5878" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5878" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5879">
+      <c r="A5879" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5879" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5879" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5880">
+      <c r="A5880" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B5880" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5880" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5880"/>
+  <dimension ref="A1:C5947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88618,6 +88618,1011 @@
         <v>11.3</v>
       </c>
     </row>
+    <row r="5881">
+      <c r="A5881" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5881" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5881" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5882">
+      <c r="A5882" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5882" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5882" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="5883">
+      <c r="A5883" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5883" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5883" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="5884">
+      <c r="A5884" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5884" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5884" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5885">
+      <c r="A5885" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5885" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5885" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5886">
+      <c r="A5886" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5886" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5886" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5887">
+      <c r="A5887" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5887" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5887" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="5888">
+      <c r="A5888" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5888" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5888" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="5889">
+      <c r="A5889" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5889" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5889" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5890">
+      <c r="A5890" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5890" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5890" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5891">
+      <c r="A5891" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5891" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5891" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5892">
+      <c r="A5892" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5892" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5892" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="5893">
+      <c r="A5893" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5893" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5893" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="5894">
+      <c r="A5894" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5894" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5894" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5895">
+      <c r="A5895" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5895" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5895" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5896">
+      <c r="A5896" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5896" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5896" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="5897">
+      <c r="A5897" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5897" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5897" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5898">
+      <c r="A5898" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5898" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5898" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5899">
+      <c r="A5899" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5899" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5899" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5900">
+      <c r="A5900" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5900" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5900" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="5901">
+      <c r="A5901" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5901" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5901" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5902">
+      <c r="A5902" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5902" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5902" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5903">
+      <c r="A5903" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5903" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5903" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="5904">
+      <c r="A5904" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5904" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5904" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="5905">
+      <c r="A5905" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5905" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5905" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5906">
+      <c r="A5906" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5906" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5906" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="5907">
+      <c r="A5907" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5907" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5907" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5908">
+      <c r="A5908" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5908" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5908" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5909">
+      <c r="A5909" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5909" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5909" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="5910">
+      <c r="A5910" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5910" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5910" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5911">
+      <c r="A5911" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5911" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5911" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5912">
+      <c r="A5912" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5912" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5912" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5913">
+      <c r="A5913" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5913" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5913" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="5914">
+      <c r="A5914" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5914" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5914" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="5915">
+      <c r="A5915" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5915" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5915" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5916">
+      <c r="A5916" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5916" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5916" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5917">
+      <c r="A5917" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5917" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5917" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="5918">
+      <c r="A5918" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5918" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5918" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5919">
+      <c r="A5919" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5919" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5919" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5920">
+      <c r="A5920" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5920" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5920" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5921">
+      <c r="A5921" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5921" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5921" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="5922">
+      <c r="A5922" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5922" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5922" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="5923">
+      <c r="A5923" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5923" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5923" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="5924">
+      <c r="A5924" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5924" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5924" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5925">
+      <c r="A5925" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5925" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5925" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="5926">
+      <c r="A5926" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5926" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5926" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5927">
+      <c r="A5927" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5927" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5927" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="5928">
+      <c r="A5928" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5928" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5928" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5929">
+      <c r="A5929" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5929" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5929" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="5930">
+      <c r="A5930" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5930" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5930" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="5931">
+      <c r="A5931" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5931" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5931" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5932">
+      <c r="A5932" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5932" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5932" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="5933">
+      <c r="A5933" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5933" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C5933" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5934">
+      <c r="A5934" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5934" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C5934" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="5935">
+      <c r="A5935" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5935" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C5935" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5936">
+      <c r="A5936" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5936" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C5936" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="5937">
+      <c r="A5937" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5937" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C5937" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5938">
+      <c r="A5938" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5938" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5938" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5939">
+      <c r="A5939" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5939" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C5939" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5940">
+      <c r="A5940" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5940" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C5940" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5941">
+      <c r="A5941" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5941" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C5941" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5942">
+      <c r="A5942" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5942" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C5942" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5943">
+      <c r="A5943" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5943" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5943" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5944">
+      <c r="A5944" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5944" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C5944" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="5945">
+      <c r="A5945" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5945" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C5945" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5946">
+      <c r="A5946" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5946" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5946" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="5947">
+      <c r="A5947" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5947" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C5947" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5947"/>
+  <dimension ref="A1:C6014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89623,6 +89623,1011 @@
         <v>14.9</v>
       </c>
     </row>
+    <row r="5948">
+      <c r="A5948" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5948" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C5948" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5949">
+      <c r="A5949" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5949" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C5949" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5950">
+      <c r="A5950" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5950" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C5950" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5951">
+      <c r="A5951" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5951" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C5951" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5952">
+      <c r="A5952" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5952" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C5952" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5953">
+      <c r="A5953" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5953" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C5953" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="5954">
+      <c r="A5954" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5954" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C5954" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="5955">
+      <c r="A5955" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5955" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C5955" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5956">
+      <c r="A5956" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5956" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C5956" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5957">
+      <c r="A5957" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5957" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C5957" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="5958">
+      <c r="A5958" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5958" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C5958" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5959">
+      <c r="A5959" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5959" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C5959" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="5960">
+      <c r="A5960" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5960" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5960" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5961">
+      <c r="A5961" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5961" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C5961" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5962">
+      <c r="A5962" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5962" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C5962" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="5963">
+      <c r="A5963" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5963" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C5963" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="5964">
+      <c r="A5964" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5964" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C5964" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5965">
+      <c r="A5965" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5965" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C5965" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5966">
+      <c r="A5966" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5966" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C5966" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5967">
+      <c r="A5967" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5967" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C5967" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="5968">
+      <c r="A5968" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5968" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C5968" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5969">
+      <c r="A5969" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5969" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C5969" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5970">
+      <c r="A5970" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5970" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C5970" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5971">
+      <c r="A5971" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5971" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C5971" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="5972">
+      <c r="A5972" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5972" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C5972" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5973">
+      <c r="A5973" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5973" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C5973" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5974">
+      <c r="A5974" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5974" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C5974" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5975">
+      <c r="A5975" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5975" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C5975" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="5976">
+      <c r="A5976" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5976" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C5976" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="5977">
+      <c r="A5977" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5977" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C5977" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="5978">
+      <c r="A5978" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5978" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C5978" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5979">
+      <c r="A5979" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5979" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C5979" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="5980">
+      <c r="A5980" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5980" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C5980" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5981">
+      <c r="A5981" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5981" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C5981" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="5982">
+      <c r="A5982" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5982" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5982" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="5983">
+      <c r="A5983" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5983" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C5983" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="5984">
+      <c r="A5984" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5984" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C5984" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="5985">
+      <c r="A5985" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5985" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C5985" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="5986">
+      <c r="A5986" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5986" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C5986" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5987">
+      <c r="A5987" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5987" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C5987" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5988">
+      <c r="A5988" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5988" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C5988" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="5989">
+      <c r="A5989" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5989" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C5989" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="5990">
+      <c r="A5990" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5990" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C5990" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5991">
+      <c r="A5991" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5991" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5991" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5992">
+      <c r="A5992" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5992" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C5992" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="5993">
+      <c r="A5993" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5993" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C5993" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5994">
+      <c r="A5994" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5994" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C5994" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="5995">
+      <c r="A5995" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5995" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C5995" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5996">
+      <c r="A5996" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5996" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C5996" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="5997">
+      <c r="A5997" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5997" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C5997" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="5998">
+      <c r="A5998" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5998" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C5998" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5999">
+      <c r="A5999" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B5999" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C5999" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6000">
+      <c r="A6000" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6000" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6000" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6001">
+      <c r="A6001" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6001" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6001" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6002">
+      <c r="A6002" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6002" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6002" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6003">
+      <c r="A6003" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6003" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6003" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6004">
+      <c r="A6004" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6004" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6004" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6005">
+      <c r="A6005" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6005" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6005" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6006">
+      <c r="A6006" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6006" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6006" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6007">
+      <c r="A6007" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6007" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6007" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6008">
+      <c r="A6008" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6008" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6008" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6009">
+      <c r="A6009" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6009" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6009" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6010">
+      <c r="A6010" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6010" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6010" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6011">
+      <c r="A6011" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6011" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6011" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6012">
+      <c r="A6012" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6012" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6012" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6013">
+      <c r="A6013" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6013" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6013" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6014">
+      <c r="A6014" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6014" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6014" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6014"/>
+  <dimension ref="A1:C6078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90628,6 +90628,966 @@
         <v>16.5</v>
       </c>
     </row>
+    <row r="6015">
+      <c r="A6015" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6015" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6015" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6016">
+      <c r="A6016" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6016" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6016" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6017">
+      <c r="A6017" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6017" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6017" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="6018">
+      <c r="A6018" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6018" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6018" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="6019">
+      <c r="A6019" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6019" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6019" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6020">
+      <c r="A6020" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6020" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6020" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="6021">
+      <c r="A6021" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6021" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6021" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6022">
+      <c r="A6022" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6022" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6022" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6023">
+      <c r="A6023" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6023" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6023" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6024">
+      <c r="A6024" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6024" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6024" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6025">
+      <c r="A6025" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6025" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6025" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="6026">
+      <c r="A6026" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6026" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6026" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="6027">
+      <c r="A6027" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6027" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6027" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6028">
+      <c r="A6028" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6028" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6028" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6029">
+      <c r="A6029" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6029" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6029" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6030">
+      <c r="A6030" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6030" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6030" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="6031">
+      <c r="A6031" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6031" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6031" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6032">
+      <c r="A6032" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6032" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6032" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6033">
+      <c r="A6033" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6033" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6033" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="6034">
+      <c r="A6034" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6034" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6034" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6035">
+      <c r="A6035" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6035" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6035" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6036">
+      <c r="A6036" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6036" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6036" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6037">
+      <c r="A6037" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6037" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6037" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6038">
+      <c r="A6038" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6038" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6038" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6039">
+      <c r="A6039" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6039" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6039" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6040">
+      <c r="A6040" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6040" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6040" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6041">
+      <c r="A6041" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6041" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6041" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6042">
+      <c r="A6042" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6042" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6042" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6043">
+      <c r="A6043" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6043" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6043" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6044">
+      <c r="A6044" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6044" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6044" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="6045">
+      <c r="A6045" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6045" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6045" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="6046">
+      <c r="A6046" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6046" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6046" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="6047">
+      <c r="A6047" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6047" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6047" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="6048">
+      <c r="A6048" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6048" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6048" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6049">
+      <c r="A6049" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6049" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6049" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="6050">
+      <c r="A6050" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6050" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6050" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="6051">
+      <c r="A6051" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6051" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6051" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6052">
+      <c r="A6052" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6052" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6052" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="6053">
+      <c r="A6053" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6053" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6053" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6054">
+      <c r="A6054" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6054" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6054" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6055">
+      <c r="A6055" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6055" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6055" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6056">
+      <c r="A6056" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6056" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6056" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="6057">
+      <c r="A6057" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6057" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6057" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="6058">
+      <c r="A6058" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6058" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6058" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6059">
+      <c r="A6059" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6059" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6059" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="6060">
+      <c r="A6060" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6060" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6060" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6061">
+      <c r="A6061" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6061" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6061" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6062">
+      <c r="A6062" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6062" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6062" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="6063">
+      <c r="A6063" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6063" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6063" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6064">
+      <c r="A6064" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6064" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6064" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6065">
+      <c r="A6065" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6065" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6065" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6066">
+      <c r="A6066" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6066" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6066" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6067">
+      <c r="A6067" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6067" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6067" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6068">
+      <c r="A6068" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6068" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6068" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6069">
+      <c r="A6069" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6069" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6069" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="6070">
+      <c r="A6070" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6070" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6070" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6071">
+      <c r="A6071" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6071" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6071" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6072">
+      <c r="A6072" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6072" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6072" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6073">
+      <c r="A6073" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6073" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6073" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6074">
+      <c r="A6074" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6074" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6074" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6075">
+      <c r="A6075" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6075" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6075" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6076">
+      <c r="A6076" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6076" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6076" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6077">
+      <c r="A6077" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6077" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6077" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="6078">
+      <c r="A6078" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6078" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6078" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6078"/>
+  <dimension ref="A1:C6143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91588,6 +91588,981 @@
         <v>15.1</v>
       </c>
     </row>
+    <row r="6079">
+      <c r="A6079" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6079" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6079" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6080">
+      <c r="A6080" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6080" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6080" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6081">
+      <c r="A6081" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6081" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6081" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="6082">
+      <c r="A6082" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6082" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6082" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6083">
+      <c r="A6083" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6083" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6083" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6084">
+      <c r="A6084" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6084" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6084" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6085">
+      <c r="A6085" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6085" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6085" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="6086">
+      <c r="A6086" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6086" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6086" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6087">
+      <c r="A6087" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6087" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6087" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6088">
+      <c r="A6088" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6088" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6088" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6089">
+      <c r="A6089" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6089" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6089" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6090">
+      <c r="A6090" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6090" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6090" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6091">
+      <c r="A6091" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6091" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6091" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="6092">
+      <c r="A6092" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6092" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6092" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="6093">
+      <c r="A6093" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6093" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6093" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6094">
+      <c r="A6094" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6094" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6094" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6095">
+      <c r="A6095" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6095" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6095" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6096">
+      <c r="A6096" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6096" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6096" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6097">
+      <c r="A6097" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6097" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6097" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="6098">
+      <c r="A6098" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6098" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6098" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="6099">
+      <c r="A6099" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6099" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6099" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="6100">
+      <c r="A6100" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6100" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6100" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6101">
+      <c r="A6101" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6101" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6101" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6102">
+      <c r="A6102" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6102" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6102" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6103">
+      <c r="A6103" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6103" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6103" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6104">
+      <c r="A6104" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6104" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6104" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6105">
+      <c r="A6105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6105" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6105" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6106">
+      <c r="A6106" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6106" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6106" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6107">
+      <c r="A6107" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6107" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6107" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6108">
+      <c r="A6108" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6108" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6108" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="6109">
+      <c r="A6109" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6109" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6109" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="6110">
+      <c r="A6110" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6110" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6110" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6111">
+      <c r="A6111" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6111" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6111" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="6112">
+      <c r="A6112" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6112" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6112" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6113">
+      <c r="A6113" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6113" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6113" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="6114">
+      <c r="A6114" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6114" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6114" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6115">
+      <c r="A6115" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6115" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6115" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="6116">
+      <c r="A6116" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6116" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6116" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="6117">
+      <c r="A6117" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6117" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6117" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6118">
+      <c r="A6118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6118" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6118" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6119">
+      <c r="A6119" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6119" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6119" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6120">
+      <c r="A6120" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6120" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6120" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6121">
+      <c r="A6121" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6121" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6121" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="6122">
+      <c r="A6122" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6122" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6122" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="6123">
+      <c r="A6123" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6123" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6123" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6124">
+      <c r="A6124" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6124" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6124" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="6125">
+      <c r="A6125" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6125" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6125" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6126">
+      <c r="A6126" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6126" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6126" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6127">
+      <c r="A6127" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6127" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6127" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="6128">
+      <c r="A6128" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6128" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6128" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6129">
+      <c r="A6129" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6129" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6129" t="n">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="6130">
+      <c r="A6130" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6130" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6130" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6131">
+      <c r="A6131" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6131" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6131" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6132">
+      <c r="A6132" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6132" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6132" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6133">
+      <c r="A6133" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6133" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6133" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6134">
+      <c r="A6134" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6134" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6134" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6135">
+      <c r="A6135" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6135" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6135" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6136">
+      <c r="A6136" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6136" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6136" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="6137">
+      <c r="A6137" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6137" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6137" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6138">
+      <c r="A6138" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6138" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6138" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6139">
+      <c r="A6139" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6139" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6139" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6140">
+      <c r="A6140" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6140" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6140" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6141">
+      <c r="A6141" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6141" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6141" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6142">
+      <c r="A6142" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6142" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6142" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6143">
+      <c r="A6143" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6143" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6143" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6143"/>
+  <dimension ref="A1:C6209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92563,6 +92563,996 @@
         <v>15.8</v>
       </c>
     </row>
+    <row r="6144">
+      <c r="A6144" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6144" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6144" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6145">
+      <c r="A6145" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6145" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6145" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6146">
+      <c r="A6146" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6146" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6146" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6147">
+      <c r="A6147" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6147" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6147" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6148">
+      <c r="A6148" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6148" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6148" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="6149">
+      <c r="A6149" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6149" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6149" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6150">
+      <c r="A6150" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6150" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6150" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6151">
+      <c r="A6151" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6151" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6151" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6152">
+      <c r="A6152" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6152" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6152" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6153">
+      <c r="A6153" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6153" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6153" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="6154">
+      <c r="A6154" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6154" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6154" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6155">
+      <c r="A6155" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6155" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6155" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6156">
+      <c r="A6156" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6156" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6156" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="6157">
+      <c r="A6157" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6157" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6157" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="6158">
+      <c r="A6158" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6158" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6158" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6159">
+      <c r="A6159" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6159" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6159" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6160">
+      <c r="A6160" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6160" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6160" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6161">
+      <c r="A6161" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6161" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6161" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="6162">
+      <c r="A6162" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6162" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6162" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="6163">
+      <c r="A6163" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6163" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6163" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="6164">
+      <c r="A6164" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6164" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6164" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6165">
+      <c r="A6165" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6165" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6165" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="6166">
+      <c r="A6166" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6166" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6166" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6167">
+      <c r="A6167" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6167" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6167" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6168">
+      <c r="A6168" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6168" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6168" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6169">
+      <c r="A6169" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6169" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6169" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6170">
+      <c r="A6170" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6170" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6170" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6171">
+      <c r="A6171" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6171" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6171" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="6172">
+      <c r="A6172" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6172" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6172" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6173">
+      <c r="A6173" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6173" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6173" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="6174">
+      <c r="A6174" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6174" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6174" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6175">
+      <c r="A6175" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6175" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6175" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="6176">
+      <c r="A6176" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6176" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6176" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6177">
+      <c r="A6177" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6177" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6177" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6178">
+      <c r="A6178" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6178" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6178" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6179">
+      <c r="A6179" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6179" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6179" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="6180">
+      <c r="A6180" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6180" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6180" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6181">
+      <c r="A6181" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6181" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6181" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6182">
+      <c r="A6182" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6182" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6182" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="6183">
+      <c r="A6183" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6183" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6183" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6184">
+      <c r="A6184" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6184" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6184" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6185">
+      <c r="A6185" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6185" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6185" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6186">
+      <c r="A6186" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6186" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6186" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6187">
+      <c r="A6187" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6187" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6187" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="6188">
+      <c r="A6188" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6188" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6188" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="6189">
+      <c r="A6189" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6189" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6189" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6190">
+      <c r="A6190" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6190" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6190" t="n">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="6191">
+      <c r="A6191" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6191" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6191" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="6192">
+      <c r="A6192" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6192" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6192" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="6193">
+      <c r="A6193" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6193" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6193" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6194">
+      <c r="A6194" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6194" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6194" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6195">
+      <c r="A6195" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6195" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6195" t="n">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="6196">
+      <c r="A6196" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6196" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6196" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="6197">
+      <c r="A6197" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6197" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6197" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6198">
+      <c r="A6198" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6198" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6198" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6199">
+      <c r="A6199" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6199" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6199" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6200">
+      <c r="A6200" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6200" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6200" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6201">
+      <c r="A6201" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6201" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6201" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6202">
+      <c r="A6202" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6202" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6202" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6203">
+      <c r="A6203" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6203" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6203" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6204">
+      <c r="A6204" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6204" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6204" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="6205">
+      <c r="A6205" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6205" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6205" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="6206">
+      <c r="A6206" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6206" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6206" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6207">
+      <c r="A6207" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6207" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6207" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="6208">
+      <c r="A6208" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6208" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6208" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6209">
+      <c r="A6209" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6209" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6209" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6209"/>
+  <dimension ref="A1:C6275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93553,6 +93553,996 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6210">
+      <c r="A6210" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6210" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6210" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6211">
+      <c r="A6211" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6211" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6211" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6212">
+      <c r="A6212" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6212" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6212" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6213">
+      <c r="A6213" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6213" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6213" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6214">
+      <c r="A6214" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6214" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6214" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6215">
+      <c r="A6215" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6215" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6215" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="6216">
+      <c r="A6216" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6216" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6216" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6217">
+      <c r="A6217" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6217" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6217" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6218">
+      <c r="A6218" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6218" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6218" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6219">
+      <c r="A6219" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6219" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6219" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="6220">
+      <c r="A6220" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6220" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6220" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6221">
+      <c r="A6221" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6221" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6221" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6222">
+      <c r="A6222" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6222" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6222" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6223">
+      <c r="A6223" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6223" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6223" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6224">
+      <c r="A6224" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6224" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6224" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="6225">
+      <c r="A6225" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6225" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6225" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6226">
+      <c r="A6226" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6226" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6226" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="6227">
+      <c r="A6227" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6227" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6227" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6228">
+      <c r="A6228" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6228" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6228" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="6229">
+      <c r="A6229" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6229" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6229" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="6230">
+      <c r="A6230" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6230" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6230" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="6231">
+      <c r="A6231" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6231" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6231" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="6232">
+      <c r="A6232" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6232" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6232" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6233">
+      <c r="A6233" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6233" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6233" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="6234">
+      <c r="A6234" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6234" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6234" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6235">
+      <c r="A6235" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6235" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6235" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="6236">
+      <c r="A6236" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6236" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6236" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6237">
+      <c r="A6237" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6237" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6237" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6238">
+      <c r="A6238" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6238" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6238" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="6239">
+      <c r="A6239" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6239" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6239" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6240">
+      <c r="A6240" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6240" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6240" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6241">
+      <c r="A6241" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6241" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6241" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6242">
+      <c r="A6242" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6242" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6242" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="6243">
+      <c r="A6243" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6243" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6243" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6244">
+      <c r="A6244" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6244" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6244" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6245">
+      <c r="A6245" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6245" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6245" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6246">
+      <c r="A6246" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6246" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6246" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6247">
+      <c r="A6247" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6247" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6247" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6248">
+      <c r="A6248" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6248" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6248" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6249">
+      <c r="A6249" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6249" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6249" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6250">
+      <c r="A6250" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6250" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6250" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6251">
+      <c r="A6251" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6251" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6251" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6252">
+      <c r="A6252" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6252" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6252" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6253">
+      <c r="A6253" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6253" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6253" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="6254">
+      <c r="A6254" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6254" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6254" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6255">
+      <c r="A6255" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6255" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6255" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6256">
+      <c r="A6256" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6256" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6256" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="6257">
+      <c r="A6257" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6257" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6257" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6258">
+      <c r="A6258" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6258" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6258" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6259">
+      <c r="A6259" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6259" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6259" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6260">
+      <c r="A6260" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6260" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6260" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6261">
+      <c r="A6261" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6261" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6261" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6262">
+      <c r="A6262" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6262" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6262" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6263">
+      <c r="A6263" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6263" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6263" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6264">
+      <c r="A6264" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6264" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6264" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6265">
+      <c r="A6265" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6265" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6265" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6266">
+      <c r="A6266" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6266" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6266" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6267">
+      <c r="A6267" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6267" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6267" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6268">
+      <c r="A6268" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6268" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6268" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6269">
+      <c r="A6269" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6269" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6269" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="6270">
+      <c r="A6270" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6270" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6270" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="6271">
+      <c r="A6271" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6271" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6271" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6272">
+      <c r="A6272" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6272" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6272" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6273">
+      <c r="A6273" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6273" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6273" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6274">
+      <c r="A6274" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6274" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6274" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6275">
+      <c r="A6275" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6275" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6275" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6275"/>
+  <dimension ref="A1:C6340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94543,6 +94543,981 @@
         <v>15.4</v>
       </c>
     </row>
+    <row r="6276">
+      <c r="A6276" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6276" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6276" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6277">
+      <c r="A6277" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6277" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6277" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="6278">
+      <c r="A6278" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6278" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6278" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6279">
+      <c r="A6279" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6279" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6279" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6280">
+      <c r="A6280" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6280" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6280" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6281">
+      <c r="A6281" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6281" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6281" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6282">
+      <c r="A6282" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6282" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6282" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6283">
+      <c r="A6283" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6283" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6283" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6284">
+      <c r="A6284" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6284" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6284" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6285">
+      <c r="A6285" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6285" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6285" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6286">
+      <c r="A6286" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6286" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6286" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6287">
+      <c r="A6287" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6287" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6287" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6288">
+      <c r="A6288" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6288" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6288" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="6289">
+      <c r="A6289" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6289" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6289" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6290">
+      <c r="A6290" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6290" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6290" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6291">
+      <c r="A6291" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6291" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6291" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6292">
+      <c r="A6292" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6292" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6292" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6293">
+      <c r="A6293" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6293" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6293" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6294">
+      <c r="A6294" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6294" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6294" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="6295">
+      <c r="A6295" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6295" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6295" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="6296">
+      <c r="A6296" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6296" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6296" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6297">
+      <c r="A6297" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6297" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6297" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6298">
+      <c r="A6298" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6298" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6298" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6299">
+      <c r="A6299" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6299" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6299" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6300">
+      <c r="A6300" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6300" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6300" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6301">
+      <c r="A6301" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6301" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6301" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="6302">
+      <c r="A6302" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6302" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6302" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6303">
+      <c r="A6303" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6303" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6303" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="6304">
+      <c r="A6304" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6304" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6304" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6305">
+      <c r="A6305" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6305" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6305" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6306">
+      <c r="A6306" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6306" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6306" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="6307">
+      <c r="A6307" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6307" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6307" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6308">
+      <c r="A6308" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6308" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6308" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6309">
+      <c r="A6309" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6309" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6309" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6310">
+      <c r="A6310" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6310" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6310" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="6311">
+      <c r="A6311" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6311" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6311" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="6312">
+      <c r="A6312" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6312" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6312" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6313">
+      <c r="A6313" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6313" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6313" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6314">
+      <c r="A6314" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6314" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6314" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6315">
+      <c r="A6315" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6315" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6315" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6316">
+      <c r="A6316" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6316" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6316" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6317">
+      <c r="A6317" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6317" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6317" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="6318">
+      <c r="A6318" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6318" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6318" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="6319">
+      <c r="A6319" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6319" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6319" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6320">
+      <c r="A6320" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6320" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6320" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6321">
+      <c r="A6321" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6321" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6321" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6322">
+      <c r="A6322" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6322" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6322" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6323">
+      <c r="A6323" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6323" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6323" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="6324">
+      <c r="A6324" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6324" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6324" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6325">
+      <c r="A6325" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6325" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6325" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6326">
+      <c r="A6326" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6326" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6326" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6327">
+      <c r="A6327" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6327" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6327" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6328">
+      <c r="A6328" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6328" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6328" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6329">
+      <c r="A6329" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6329" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6329" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6330">
+      <c r="A6330" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6330" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6330" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6331">
+      <c r="A6331" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6331" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6331" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="6332">
+      <c r="A6332" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6332" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6332" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6333">
+      <c r="A6333" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6333" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6333" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6334">
+      <c r="A6334" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6334" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6334" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="6335">
+      <c r="A6335" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6335" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6335" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6336">
+      <c r="A6336" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6336" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6336" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6337">
+      <c r="A6337" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6337" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6337" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6338">
+      <c r="A6338" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6338" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6338" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="6339">
+      <c r="A6339" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6339" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6339" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6340">
+      <c r="A6340" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6340" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6340" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6340"/>
+  <dimension ref="A1:C6407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95518,6 +95518,1011 @@
         <v>15.8</v>
       </c>
     </row>
+    <row r="6341">
+      <c r="A6341" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6341" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6341" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6342">
+      <c r="A6342" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6342" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6342" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6343">
+      <c r="A6343" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6343" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6343" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6344">
+      <c r="A6344" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6344" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6344" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6345">
+      <c r="A6345" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6345" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6345" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6346">
+      <c r="A6346" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6346" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6346" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6347">
+      <c r="A6347" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6347" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6347" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="6348">
+      <c r="A6348" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6348" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6348" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6349">
+      <c r="A6349" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6349" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6349" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6350">
+      <c r="A6350" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6350" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6350" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="6351">
+      <c r="A6351" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6351" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6351" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6352">
+      <c r="A6352" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6352" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6352" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6353">
+      <c r="A6353" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6353" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6353" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="6354">
+      <c r="A6354" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6354" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6354" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6355">
+      <c r="A6355" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6355" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6355" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6356">
+      <c r="A6356" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6356" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6356" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6357">
+      <c r="A6357" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6357" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6357" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6358">
+      <c r="A6358" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6358" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6358" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6359">
+      <c r="A6359" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6359" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6359" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="6360">
+      <c r="A6360" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6360" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6360" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6361">
+      <c r="A6361" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6361" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6361" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6362">
+      <c r="A6362" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6362" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6362" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6363">
+      <c r="A6363" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6363" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6363" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="6364">
+      <c r="A6364" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6364" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6364" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="6365">
+      <c r="A6365" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6365" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6365" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6366">
+      <c r="A6366" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6366" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6366" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6367">
+      <c r="A6367" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6367" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6367" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6368">
+      <c r="A6368" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6368" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6368" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6369">
+      <c r="A6369" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6369" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6369" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="6370">
+      <c r="A6370" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6370" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6370" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6371">
+      <c r="A6371" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6371" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6371" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6372">
+      <c r="A6372" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6372" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6372" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6373">
+      <c r="A6373" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6373" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6373" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="6374">
+      <c r="A6374" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6374" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6374" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6375">
+      <c r="A6375" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6375" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6375" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="6376">
+      <c r="A6376" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6376" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6376" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="6377">
+      <c r="A6377" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6377" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6377" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="6378">
+      <c r="A6378" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6378" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6378" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="6379">
+      <c r="A6379" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6379" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6379" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6380">
+      <c r="A6380" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6380" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6380" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6381">
+      <c r="A6381" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6381" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6381" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6382">
+      <c r="A6382" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6382" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6382" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6383">
+      <c r="A6383" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6383" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6383" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6384">
+      <c r="A6384" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6384" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6384" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="6385">
+      <c r="A6385" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6385" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6385" t="n">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="6386">
+      <c r="A6386" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6386" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6386" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6387">
+      <c r="A6387" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6387" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6387" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6388">
+      <c r="A6388" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6388" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6388" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6389">
+      <c r="A6389" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6389" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6389" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6390">
+      <c r="A6390" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6390" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6390" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6391">
+      <c r="A6391" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6391" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6391" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="6392">
+      <c r="A6392" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6392" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6392" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6393">
+      <c r="A6393" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6393" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6393" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6394">
+      <c r="A6394" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6394" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6394" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="6395">
+      <c r="A6395" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6395" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6395" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6396">
+      <c r="A6396" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6396" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6396" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6397">
+      <c r="A6397" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6397" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6397" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6398">
+      <c r="A6398" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6398" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6398" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6399">
+      <c r="A6399" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6399" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6399" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6400">
+      <c r="A6400" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6400" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6400" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6401">
+      <c r="A6401" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6401" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6401" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="6402">
+      <c r="A6402" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6402" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6402" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6403">
+      <c r="A6403" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6403" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6403" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6404">
+      <c r="A6404" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6404" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6404" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6405">
+      <c r="A6405" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6405" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6405" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="6406">
+      <c r="A6406" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6406" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6406" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="6407">
+      <c r="A6407" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6407" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6407" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6407"/>
+  <dimension ref="A1:C6473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96523,6 +96523,996 @@
         <v>16.8</v>
       </c>
     </row>
+    <row r="6408">
+      <c r="A6408" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6408" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6408" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6409">
+      <c r="A6409" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6409" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6409" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6410">
+      <c r="A6410" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6410" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6410" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6411">
+      <c r="A6411" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6411" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6411" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6412">
+      <c r="A6412" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6412" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6412" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="6413">
+      <c r="A6413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6413" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6413" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="6414">
+      <c r="A6414" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6414" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6414" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6415">
+      <c r="A6415" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6415" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6415" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="6416">
+      <c r="A6416" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6416" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6416" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6417">
+      <c r="A6417" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6417" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6417" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6418">
+      <c r="A6418" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6418" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6418" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6419">
+      <c r="A6419" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6419" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6419" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6420">
+      <c r="A6420" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6420" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6420" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="6421">
+      <c r="A6421" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6421" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6421" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="6422">
+      <c r="A6422" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6422" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6422" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6423">
+      <c r="A6423" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6423" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6423" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6424">
+      <c r="A6424" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6424" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6424" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6425">
+      <c r="A6425" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6425" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6425" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6426">
+      <c r="A6426" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6426" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6426" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6427">
+      <c r="A6427" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6427" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6427" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6428">
+      <c r="A6428" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6428" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6428" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="6429">
+      <c r="A6429" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6429" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6429" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6430">
+      <c r="A6430" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6430" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6430" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6431">
+      <c r="A6431" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6431" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6431" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6432">
+      <c r="A6432" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6432" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6432" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6433">
+      <c r="A6433" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6433" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6433" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6434">
+      <c r="A6434" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6434" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6434" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="6435">
+      <c r="A6435" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6435" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6435" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="6436">
+      <c r="A6436" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6436" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6436" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6437">
+      <c r="A6437" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6437" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6437" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6438">
+      <c r="A6438" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6438" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6438" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6439">
+      <c r="A6439" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6439" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6439" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6440">
+      <c r="A6440" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6440" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6440" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6441">
+      <c r="A6441" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6441" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6441" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="6442">
+      <c r="A6442" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6442" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6442" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="6443">
+      <c r="A6443" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6443" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6443" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6444">
+      <c r="A6444" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6444" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6444" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6445">
+      <c r="A6445" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6445" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6445" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6446">
+      <c r="A6446" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6446" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6446" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6447">
+      <c r="A6447" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6447" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6447" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6448">
+      <c r="A6448" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6448" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6448" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6449">
+      <c r="A6449" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6449" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6449" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6450">
+      <c r="A6450" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6450" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6450" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6451">
+      <c r="A6451" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6451" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6451" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="6452">
+      <c r="A6452" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6452" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6452" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6453">
+      <c r="A6453" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6453" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6453" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6454">
+      <c r="A6454" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6454" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6454" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6455">
+      <c r="A6455" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6455" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6455" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6456">
+      <c r="A6456" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6456" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6456" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="6457">
+      <c r="A6457" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6457" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6457" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="6458">
+      <c r="A6458" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6458" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6458" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6459">
+      <c r="A6459" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6459" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6459" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="6460">
+      <c r="A6460" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6460" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6460" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="6461">
+      <c r="A6461" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6461" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6461" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6462">
+      <c r="A6462" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6462" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6462" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6463">
+      <c r="A6463" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6463" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6463" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6464">
+      <c r="A6464" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6464" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6464" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6465">
+      <c r="A6465" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6465" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6465" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6466">
+      <c r="A6466" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6466" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6466" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6467">
+      <c r="A6467" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6467" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6467" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6468">
+      <c r="A6468" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6468" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6468" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6469">
+      <c r="A6469" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6469" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6469" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="6470">
+      <c r="A6470" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6470" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6470" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6471">
+      <c r="A6471" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6471" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6471" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="6472">
+      <c r="A6472" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6472" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6472" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6473">
+      <c r="A6473" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6473" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6473" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6473"/>
+  <dimension ref="A1:C6540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97513,6 +97513,1011 @@
         <v>14.9</v>
       </c>
     </row>
+    <row r="6474">
+      <c r="A6474" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6474" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6474" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6475">
+      <c r="A6475" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6475" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6475" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6476">
+      <c r="A6476" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6476" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6476" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6477">
+      <c r="A6477" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6477" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6477" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6478">
+      <c r="A6478" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6478" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6478" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6479">
+      <c r="A6479" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6479" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6479" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6480">
+      <c r="A6480" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6480" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6480" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6481">
+      <c r="A6481" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6481" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6481" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6482">
+      <c r="A6482" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6482" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6482" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6483">
+      <c r="A6483" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6483" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6483" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="6484">
+      <c r="A6484" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6484" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6484" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6485">
+      <c r="A6485" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6485" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6485" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6486">
+      <c r="A6486" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6486" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6486" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6487">
+      <c r="A6487" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6487" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6487" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6488">
+      <c r="A6488" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6488" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6488" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="6489">
+      <c r="A6489" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6489" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6489" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="6490">
+      <c r="A6490" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6490" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6490" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6491">
+      <c r="A6491" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6491" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6491" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6492">
+      <c r="A6492" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6492" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6492" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6493">
+      <c r="A6493" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6493" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6493" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6494">
+      <c r="A6494" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6494" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6494" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6495">
+      <c r="A6495" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6495" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6495" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6496">
+      <c r="A6496" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6496" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6496" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6497">
+      <c r="A6497" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6497" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6497" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6498">
+      <c r="A6498" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6498" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6498" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6499">
+      <c r="A6499" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6499" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6499" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6500">
+      <c r="A6500" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6500" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6500" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6501">
+      <c r="A6501" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6501" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6501" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6502">
+      <c r="A6502" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6502" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6502" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="6503">
+      <c r="A6503" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6503" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6503" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6504">
+      <c r="A6504" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6504" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6504" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="6505">
+      <c r="A6505" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6505" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6505" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="6506">
+      <c r="A6506" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6506" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6506" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="6507">
+      <c r="A6507" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6507" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6507" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6508">
+      <c r="A6508" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6508" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6508" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="6509">
+      <c r="A6509" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6509" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6509" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="6510">
+      <c r="A6510" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6510" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6510" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="6511">
+      <c r="A6511" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6511" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6511" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="6512">
+      <c r="A6512" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6512" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6512" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6513">
+      <c r="A6513" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6513" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6513" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6514">
+      <c r="A6514" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6514" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6514" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6515">
+      <c r="A6515" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6515" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6515" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6516">
+      <c r="A6516" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6516" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6516" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6517">
+      <c r="A6517" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6517" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6517" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="6518">
+      <c r="A6518" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6518" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6518" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="6519">
+      <c r="A6519" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6519" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6519" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6520">
+      <c r="A6520" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6520" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6520" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6521">
+      <c r="A6521" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6521" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6521" t="n">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="6522">
+      <c r="A6522" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6522" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6522" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="6523">
+      <c r="A6523" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6523" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6523" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="6524">
+      <c r="A6524" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6524" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6524" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6525">
+      <c r="A6525" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6525" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6525" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="6526">
+      <c r="A6526" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6526" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6526" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6527">
+      <c r="A6527" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6527" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6527" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="6528">
+      <c r="A6528" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6528" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6528" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6529">
+      <c r="A6529" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6529" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6529" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6530">
+      <c r="A6530" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6530" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6530" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6531">
+      <c r="A6531" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6531" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6531" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6532">
+      <c r="A6532" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6532" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6532" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6533">
+      <c r="A6533" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6533" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6533" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6534">
+      <c r="A6534" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6534" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6534" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6535">
+      <c r="A6535" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6535" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6535" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="6536">
+      <c r="A6536" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6536" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6536" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6537">
+      <c r="A6537" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6537" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6537" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6538">
+      <c r="A6538" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6538" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6538" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6539">
+      <c r="A6539" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6539" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6539" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6540">
+      <c r="A6540" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6540" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6540" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6540"/>
+  <dimension ref="A1:C6605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98518,6 +98518,981 @@
         <v>15</v>
       </c>
     </row>
+    <row r="6541">
+      <c r="A6541" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6541" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6541" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6542">
+      <c r="A6542" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6542" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6542" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6543">
+      <c r="A6543" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6543" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6543" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="6544">
+      <c r="A6544" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6544" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6544" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6545">
+      <c r="A6545" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6545" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6545" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6546">
+      <c r="A6546" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6546" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6546" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6547">
+      <c r="A6547" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6547" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6547" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6548">
+      <c r="A6548" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6548" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6548" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="6549">
+      <c r="A6549" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6549" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6549" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6550">
+      <c r="A6550" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6550" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6550" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="6551">
+      <c r="A6551" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6551" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6551" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6552">
+      <c r="A6552" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6552" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6552" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6553">
+      <c r="A6553" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6553" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6553" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6554">
+      <c r="A6554" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6554" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6554" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6555">
+      <c r="A6555" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6555" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6555" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6556">
+      <c r="A6556" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6556" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6556" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6557">
+      <c r="A6557" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6557" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6557" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6558">
+      <c r="A6558" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6558" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6558" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="6559">
+      <c r="A6559" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6559" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6559" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="6560">
+      <c r="A6560" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6560" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6560" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6561">
+      <c r="A6561" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6561" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6561" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6562">
+      <c r="A6562" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6562" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6562" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6563">
+      <c r="A6563" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6563" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6563" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6564">
+      <c r="A6564" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6564" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6564" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6565">
+      <c r="A6565" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6565" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6565" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6566">
+      <c r="A6566" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6566" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6566" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6567">
+      <c r="A6567" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6567" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6567" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6568">
+      <c r="A6568" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6568" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6568" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6569">
+      <c r="A6569" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6569" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6569" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6570">
+      <c r="A6570" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6570" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6570" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6571">
+      <c r="A6571" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6571" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6571" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6572">
+      <c r="A6572" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6572" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6572" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6573">
+      <c r="A6573" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6573" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6573" t="n">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="6574">
+      <c r="A6574" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6574" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6574" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6575">
+      <c r="A6575" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6575" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6575" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="6576">
+      <c r="A6576" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6576" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6576" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="6577">
+      <c r="A6577" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6577" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6577" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="6578">
+      <c r="A6578" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6578" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6578" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6579">
+      <c r="A6579" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6579" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6579" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="6580">
+      <c r="A6580" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6580" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6580" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6581">
+      <c r="A6581" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6581" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6581" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="6582">
+      <c r="A6582" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6582" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6582" t="n">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="6583">
+      <c r="A6583" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6583" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6583" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="6584">
+      <c r="A6584" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6584" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6584" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6585">
+      <c r="A6585" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6585" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6585" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6586">
+      <c r="A6586" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6586" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6586" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="6587">
+      <c r="A6587" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6587" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6587" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6588">
+      <c r="A6588" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6588" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6588" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="6589">
+      <c r="A6589" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6589" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6589" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6590">
+      <c r="A6590" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6590" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6590" t="n">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6591">
+      <c r="A6591" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6591" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6591" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6592">
+      <c r="A6592" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6592" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6592" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6593">
+      <c r="A6593" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6593" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6593" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6594">
+      <c r="A6594" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6594" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6594" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="6595">
+      <c r="A6595" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6595" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6595" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6596">
+      <c r="A6596" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6596" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6596" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6597">
+      <c r="A6597" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6597" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6597" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6598">
+      <c r="A6598" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6598" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6598" t="n">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="6599">
+      <c r="A6599" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6599" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6599" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6600">
+      <c r="A6600" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6600" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6600" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="6601">
+      <c r="A6601" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6601" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6601" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6602">
+      <c r="A6602" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6602" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6602" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6603">
+      <c r="A6603" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6603" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6603" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6604">
+      <c r="A6604" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6604" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6604" t="n">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="6605">
+      <c r="A6605" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6605" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6605" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6605"/>
+  <dimension ref="A1:C6670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -99493,6 +99493,981 @@
         <v>13</v>
       </c>
     </row>
+    <row r="6606">
+      <c r="A6606" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6606" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6606" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6607">
+      <c r="A6607" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6607" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6607" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="6608">
+      <c r="A6608" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6608" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6608" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="6609">
+      <c r="A6609" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6609" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6609" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="6610">
+      <c r="A6610" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6610" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6610" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6611">
+      <c r="A6611" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6611" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6611" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="6612">
+      <c r="A6612" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6612" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6612" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6613">
+      <c r="A6613" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6613" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6613" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="6614">
+      <c r="A6614" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6614" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6614" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="6615">
+      <c r="A6615" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6615" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6615" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="6616">
+      <c r="A6616" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6616" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6616" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="6617">
+      <c r="A6617" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6617" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6617" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6618">
+      <c r="A6618" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6618" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6618" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6619">
+      <c r="A6619" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6619" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6619" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="6620">
+      <c r="A6620" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6620" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6620" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="6621">
+      <c r="A6621" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6621" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6621" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="6622">
+      <c r="A6622" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6622" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6622" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6623">
+      <c r="A6623" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6623" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6623" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="6624">
+      <c r="A6624" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6624" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6624" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="6625">
+      <c r="A6625" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6625" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6625" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="6626">
+      <c r="A6626" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6626" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6626" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="6627">
+      <c r="A6627" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6627" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6627" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="6628">
+      <c r="A6628" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6628" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6628" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6629">
+      <c r="A6629" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6629" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6629" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6630">
+      <c r="A6630" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6630" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6630" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6631">
+      <c r="A6631" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6631" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6631" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6632">
+      <c r="A6632" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6632" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6632" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="6633">
+      <c r="A6633" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6633" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6633" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6634">
+      <c r="A6634" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6634" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6634" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6635">
+      <c r="A6635" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6635" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6635" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6636">
+      <c r="A6636" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6636" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6636" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6637">
+      <c r="A6637" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6637" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6637" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6638">
+      <c r="A6638" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6638" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6638" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="6639">
+      <c r="A6639" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6639" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6639" t="n">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="6640">
+      <c r="A6640" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6640" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6640" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6641">
+      <c r="A6641" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6641" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6641" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="6642">
+      <c r="A6642" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6642" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6642" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="6643">
+      <c r="A6643" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6643" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6643" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6644">
+      <c r="A6644" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6644" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6644" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6645">
+      <c r="A6645" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6645" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6645" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="6646">
+      <c r="A6646" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6646" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6646" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6647">
+      <c r="A6647" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6647" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6647" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="6648">
+      <c r="A6648" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6648" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6648" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="6649">
+      <c r="A6649" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6649" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6649" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6650">
+      <c r="A6650" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6650" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6650" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="6651">
+      <c r="A6651" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6651" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6651" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="6652">
+      <c r="A6652" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6652" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6652" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="6653">
+      <c r="A6653" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6653" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6653" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6654">
+      <c r="A6654" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6654" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6654" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6655">
+      <c r="A6655" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6655" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6655" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6656">
+      <c r="A6656" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6656" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6656" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6657">
+      <c r="A6657" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6657" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6657" t="n">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6658">
+      <c r="A6658" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6658" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6658" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="6659">
+      <c r="A6659" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6659" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6659" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="6660">
+      <c r="A6660" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6660" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6660" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="6661">
+      <c r="A6661" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6661" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6661" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="6662">
+      <c r="A6662" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6662" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6662" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6663">
+      <c r="A6663" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6663" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6663" t="n">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="6664">
+      <c r="A6664" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6664" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6664" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6665">
+      <c r="A6665" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6665" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6665" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6666">
+      <c r="A6666" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6666" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6666" t="n">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6667">
+      <c r="A6667" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6667" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6667" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6668">
+      <c r="A6668" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6668" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6668" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6669">
+      <c r="A6669" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6669" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6669" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6670">
+      <c r="A6670" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6670" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6670" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6670"/>
+  <dimension ref="A1:C6736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100468,6 +100468,996 @@
         <v>11</v>
       </c>
     </row>
+    <row r="6671">
+      <c r="A6671" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6671" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6671" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6672">
+      <c r="A6672" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6672" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6672" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="6673">
+      <c r="A6673" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6673" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6673" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="6674">
+      <c r="A6674" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6674" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6674" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6675">
+      <c r="A6675" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6675" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6675" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="6676">
+      <c r="A6676" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6676" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6676" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="6677">
+      <c r="A6677" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6677" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6677" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6678">
+      <c r="A6678" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6678" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6678" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="6679">
+      <c r="A6679" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6679" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6679" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6680">
+      <c r="A6680" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6680" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6680" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6681">
+      <c r="A6681" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6681" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6681" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="6682">
+      <c r="A6682" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6682" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6682" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6683">
+      <c r="A6683" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6683" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6683" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6684">
+      <c r="A6684" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6684" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6684" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6685">
+      <c r="A6685" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6685" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6685" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="6686">
+      <c r="A6686" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6686" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6686" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="6687">
+      <c r="A6687" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6687" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6687" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="6688">
+      <c r="A6688" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6688" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6688" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6689">
+      <c r="A6689" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6689" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6689" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6690">
+      <c r="A6690" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6690" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6690" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="6691">
+      <c r="A6691" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6691" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6691" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6692">
+      <c r="A6692" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6692" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6692" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6693">
+      <c r="A6693" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6693" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6693" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6694">
+      <c r="A6694" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6694" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6694" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="6695">
+      <c r="A6695" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6695" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6695" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="6696">
+      <c r="A6696" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6696" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6696" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="6697">
+      <c r="A6697" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6697" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6697" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="6698">
+      <c r="A6698" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6698" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6698" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="6699">
+      <c r="A6699" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6699" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6699" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="6700">
+      <c r="A6700" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6700" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6700" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="6701">
+      <c r="A6701" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6701" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6701" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="6702">
+      <c r="A6702" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6702" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6702" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="6703">
+      <c r="A6703" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6703" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6703" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6704">
+      <c r="A6704" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6704" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6704" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="6705">
+      <c r="A6705" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6705" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6705" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="6706">
+      <c r="A6706" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6706" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6706" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="6707">
+      <c r="A6707" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6707" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6707" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="6708">
+      <c r="A6708" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6708" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6708" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="6709">
+      <c r="A6709" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6709" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6709" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6710">
+      <c r="A6710" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6710" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6710" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="6711">
+      <c r="A6711" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6711" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6711" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="6712">
+      <c r="A6712" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6712" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6712" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="6713">
+      <c r="A6713" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6713" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6713" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="6714">
+      <c r="A6714" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6714" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6714" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6715">
+      <c r="A6715" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6715" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6715" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="6716">
+      <c r="A6716" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6716" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6716" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="6717">
+      <c r="A6717" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6717" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6717" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="6718">
+      <c r="A6718" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6718" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6718" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="6719">
+      <c r="A6719" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6719" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6719" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6720">
+      <c r="A6720" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6720" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6720" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="6721">
+      <c r="A6721" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6721" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6721" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6722">
+      <c r="A6722" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6722" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6722" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6723">
+      <c r="A6723" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6723" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6723" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6724">
+      <c r="A6724" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6724" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6724" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="6725">
+      <c r="A6725" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6725" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6725" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6726">
+      <c r="A6726" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6726" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6726" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="6727">
+      <c r="A6727" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6727" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6727" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="6728">
+      <c r="A6728" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6728" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6728" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6729">
+      <c r="A6729" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6729" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6729" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6730">
+      <c r="A6730" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6730" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6730" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="6731">
+      <c r="A6731" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6731" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6731" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6732">
+      <c r="A6732" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6732" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6732" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="6733">
+      <c r="A6733" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6733" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6733" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6734">
+      <c r="A6734" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6734" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6734" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6735">
+      <c r="A6735" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6735" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6735" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="6736">
+      <c r="A6736" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6736" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6736" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6736"/>
+  <dimension ref="A1:C6802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101458,6 +101458,996 @@
         <v>12.2</v>
       </c>
     </row>
+    <row r="6737">
+      <c r="A6737" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6737" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6737" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6738">
+      <c r="A6738" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6738" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6738" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="6739">
+      <c r="A6739" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6739" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6739" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="6740">
+      <c r="A6740" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6740" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6740" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="6741">
+      <c r="A6741" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6741" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6741" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6742">
+      <c r="A6742" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6742" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6742" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="6743">
+      <c r="A6743" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6743" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6743" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="6744">
+      <c r="A6744" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6744" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6744" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6745">
+      <c r="A6745" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6745" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6745" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6746">
+      <c r="A6746" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6746" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6746" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="6747">
+      <c r="A6747" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6747" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6747" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="6748">
+      <c r="A6748" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6748" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6748" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="6749">
+      <c r="A6749" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6749" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6749" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="6750">
+      <c r="A6750" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6750" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6750" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="6751">
+      <c r="A6751" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6751" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6751" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="6752">
+      <c r="A6752" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6752" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6752" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="6753">
+      <c r="A6753" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6753" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6753" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="6754">
+      <c r="A6754" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6754" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6754" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6755">
+      <c r="A6755" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6755" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6755" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="6756">
+      <c r="A6756" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6756" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6756" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="6757">
+      <c r="A6757" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6757" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6757" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6758">
+      <c r="A6758" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6758" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6758" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="6759">
+      <c r="A6759" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6759" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6759" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="6760">
+      <c r="A6760" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6760" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6760" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="6761">
+      <c r="A6761" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6761" t="inlineStr">
+        <is>
+          <t>Kukuljanovo</t>
+        </is>
+      </c>
+      <c r="C6761" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6762">
+      <c r="A6762" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6762" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6762" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="6763">
+      <c r="A6763" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6763" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6763" t="n">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="6764">
+      <c r="A6764" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6764" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6764" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="6765">
+      <c r="A6765" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6765" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6765" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="6766">
+      <c r="A6766" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6766" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6766" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="6767">
+      <c r="A6767" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6767" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6767" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="6768">
+      <c r="A6768" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6768" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6768" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="6769">
+      <c r="A6769" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6769" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6769" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="6770">
+      <c r="A6770" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6770" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6770" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="6771">
+      <c r="A6771" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6771" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6771" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="6772">
+      <c r="A6772" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6772" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6772" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="6773">
+      <c r="A6773" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6773" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6773" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6774">
+      <c r="A6774" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6774" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6774" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6775">
+      <c r="A6775" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6775" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6775" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6776">
+      <c r="A6776" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6776" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6776" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6777">
+      <c r="A6777" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6777" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6777" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6778">
+      <c r="A6778" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6778" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6778" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="6779">
+      <c r="A6779" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6779" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6779" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="6780">
+      <c r="A6780" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6780" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6780" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="6781">
+      <c r="A6781" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6781" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6781" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="6782">
+      <c r="A6782" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6782" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6782" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="6783">
+      <c r="A6783" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6783" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6783" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6784">
+      <c r="A6784" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6784" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6784" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6785">
+      <c r="A6785" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6785" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6785" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6786">
+      <c r="A6786" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6786" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6786" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="6787">
+      <c r="A6787" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6787" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6787" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="6788">
+      <c r="A6788" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6788" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6788" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="6789">
+      <c r="A6789" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6789" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6789" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="6790">
+      <c r="A6790" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6790" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6790" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="6791">
+      <c r="A6791" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6791" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6791" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6792">
+      <c r="A6792" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6792" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6792" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="6793">
+      <c r="A6793" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6793" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6793" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="6794">
+      <c r="A6794" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6794" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6794" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6795">
+      <c r="A6795" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6795" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6795" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="6796">
+      <c r="A6796" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6796" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6796" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6797">
+      <c r="A6797" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6797" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6797" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="6798">
+      <c r="A6798" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6798" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6798" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6799">
+      <c r="A6799" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6799" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6799" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="6800">
+      <c r="A6800" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6800" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6800" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="6801">
+      <c r="A6801" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6801" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6801" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="6802">
+      <c r="A6802" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6802" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6802" t="n">
+        <v>10.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6802"/>
+  <dimension ref="A1:C6868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102448,6 +102448,996 @@
         <v>10.2</v>
       </c>
     </row>
+    <row r="6803">
+      <c r="A6803" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6803" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6803" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6804">
+      <c r="A6804" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6804" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6804" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="6805">
+      <c r="A6805" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6805" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6805" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="6806">
+      <c r="A6806" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6806" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6806" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="6807">
+      <c r="A6807" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6807" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6807" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="6808">
+      <c r="A6808" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6808" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6808" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="6809">
+      <c r="A6809" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6809" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6809" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6810">
+      <c r="A6810" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6810" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6810" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="6811">
+      <c r="A6811" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6811" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6811" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6812">
+      <c r="A6812" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6812" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6812" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="6813">
+      <c r="A6813" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6813" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6813" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6814">
+      <c r="A6814" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6814" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6814" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6815">
+      <c r="A6815" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6815" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6815" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="6816">
+      <c r="A6816" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6816" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6816" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6817">
+      <c r="A6817" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6817" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6817" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6818">
+      <c r="A6818" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6818" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6818" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="6819">
+      <c r="A6819" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6819" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6819" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6820">
+      <c r="A6820" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6820" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6820" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="6821">
+      <c r="A6821" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6821" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6821" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="6822">
+      <c r="A6822" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6822" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6822" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="6823">
+      <c r="A6823" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6823" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6823" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="6824">
+      <c r="A6824" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6824" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6824" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6825">
+      <c r="A6825" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6825" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6825" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6826">
+      <c r="A6826" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6826" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6826" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="6827">
+      <c r="A6827" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6827" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6827" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="6828">
+      <c r="A6828" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6828" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6828" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="6829">
+      <c r="A6829" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6829" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6829" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="6830">
+      <c r="A6830" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6830" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6830" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="6831">
+      <c r="A6831" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6831" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6831" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="6832">
+      <c r="A6832" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6832" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6832" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6833">
+      <c r="A6833" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6833" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6833" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="6834">
+      <c r="A6834" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6834" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6834" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="6835">
+      <c r="A6835" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6835" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6835" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6836">
+      <c r="A6836" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6836" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6836" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="6837">
+      <c r="A6837" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6837" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6837" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="6838">
+      <c r="A6838" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6838" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6838" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="6839">
+      <c r="A6839" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6839" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6839" t="n">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="6840">
+      <c r="A6840" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6840" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6840" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="6841">
+      <c r="A6841" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6841" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6841" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="6842">
+      <c r="A6842" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6842" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6842" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="6843">
+      <c r="A6843" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6843" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6843" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="6844">
+      <c r="A6844" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6844" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6844" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6845">
+      <c r="A6845" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6845" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6845" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6846">
+      <c r="A6846" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6846" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6846" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="6847">
+      <c r="A6847" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6847" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6847" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6848">
+      <c r="A6848" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6848" t="inlineStr">
+        <is>
+          <t>Račinovci</t>
+        </is>
+      </c>
+      <c r="C6848" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="6849">
+      <c r="A6849" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6849" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6849" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="6850">
+      <c r="A6850" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6850" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6850" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="6851">
+      <c r="A6851" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6851" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6851" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6852">
+      <c r="A6852" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6852" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6852" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6853">
+      <c r="A6853" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6853" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6853" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="6854">
+      <c r="A6854" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6854" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6854" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="6855">
+      <c r="A6855" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6855" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6855" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="6856">
+      <c r="A6856" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6856" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6856" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6857">
+      <c r="A6857" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6857" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6857" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="6858">
+      <c r="A6858" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6858" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6858" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="6859">
+      <c r="A6859" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6859" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6859" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="6860">
+      <c r="A6860" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6860" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6860" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6861">
+      <c r="A6861" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6861" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6861" t="n">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="6862">
+      <c r="A6862" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6862" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6862" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="6863">
+      <c r="A6863" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6863" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6863" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="6864">
+      <c r="A6864" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6864" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6864" t="n">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="6865">
+      <c r="A6865" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6865" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6865" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="6866">
+      <c r="A6866" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6866" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6866" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="6867">
+      <c r="A6867" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6867" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6867" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="6868">
+      <c r="A6868" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6868" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6868" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6868"/>
+  <dimension ref="A1:C6933"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103438,6 +103438,981 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6869">
+      <c r="A6869" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6869" t="inlineStr">
+        <is>
+          <t>Bakar</t>
+        </is>
+      </c>
+      <c r="C6869" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6870">
+      <c r="A6870" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6870" t="inlineStr">
+        <is>
+          <t>Bednja</t>
+        </is>
+      </c>
+      <c r="C6870" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6871">
+      <c r="A6871" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6871" t="inlineStr">
+        <is>
+          <t>Beli Manastir</t>
+        </is>
+      </c>
+      <c r="C6871" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="6872">
+      <c r="A6872" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6872" t="inlineStr">
+        <is>
+          <t>Bilje</t>
+        </is>
+      </c>
+      <c r="C6872" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="6873">
+      <c r="A6873" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6873" t="inlineStr">
+        <is>
+          <t>Bilogora</t>
+        </is>
+      </c>
+      <c r="C6873" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="6874">
+      <c r="A6874" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6874" t="inlineStr">
+        <is>
+          <t>Bjelovar</t>
+        </is>
+      </c>
+      <c r="C6874" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6875">
+      <c r="A6875" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6875" t="inlineStr">
+        <is>
+          <t>Božava</t>
+        </is>
+      </c>
+      <c r="C6875" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="6876">
+      <c r="A6876" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6876" t="inlineStr">
+        <is>
+          <t>Brestovac</t>
+        </is>
+      </c>
+      <c r="C6876" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="6877">
+      <c r="A6877" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6877" t="inlineStr">
+        <is>
+          <t>Daruvar</t>
+        </is>
+      </c>
+      <c r="C6877" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="6878">
+      <c r="A6878" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6878" t="inlineStr">
+        <is>
+          <t>Delnice</t>
+        </is>
+      </c>
+      <c r="C6878" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="6879">
+      <c r="A6879" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6879" t="inlineStr">
+        <is>
+          <t>Đakovo</t>
+        </is>
+      </c>
+      <c r="C6879" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="6880">
+      <c r="A6880" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6880" t="inlineStr">
+        <is>
+          <t>Dubrovnik</t>
+        </is>
+      </c>
+      <c r="C6880" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="6881">
+      <c r="A6881" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6881" t="inlineStr">
+        <is>
+          <t>Dubrovnik-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6881" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="6882">
+      <c r="A6882" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6882" t="inlineStr">
+        <is>
+          <t>RC Gorice (kod Nove Gradiške)</t>
+        </is>
+      </c>
+      <c r="C6882" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="6883">
+      <c r="A6883" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6883" t="inlineStr">
+        <is>
+          <t>Gospić</t>
+        </is>
+      </c>
+      <c r="C6883" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6884">
+      <c r="A6884" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6884" t="inlineStr">
+        <is>
+          <t>Gračac</t>
+        </is>
+      </c>
+      <c r="C6884" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="6885">
+      <c r="A6885" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6885" t="inlineStr">
+        <is>
+          <t>RC Gradište (kod Županje)</t>
+        </is>
+      </c>
+      <c r="C6885" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="6886">
+      <c r="A6886" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6886" t="inlineStr">
+        <is>
+          <t>Ilok</t>
+        </is>
+      </c>
+      <c r="C6886" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="6887">
+      <c r="A6887" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6887" t="inlineStr">
+        <is>
+          <t>Imotski</t>
+        </is>
+      </c>
+      <c r="C6887" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="6888">
+      <c r="A6888" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6888" t="inlineStr">
+        <is>
+          <t>Karlovac</t>
+        </is>
+      </c>
+      <c r="C6888" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="6889">
+      <c r="A6889" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6889" t="inlineStr">
+        <is>
+          <t>Knin</t>
+        </is>
+      </c>
+      <c r="C6889" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="6890">
+      <c r="A6890" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6890" t="inlineStr">
+        <is>
+          <t>Komiža</t>
+        </is>
+      </c>
+      <c r="C6890" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6891">
+      <c r="A6891" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6891" t="inlineStr">
+        <is>
+          <t>Krapina</t>
+        </is>
+      </c>
+      <c r="C6891" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="6892">
+      <c r="A6892" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6892" t="inlineStr">
+        <is>
+          <t>Križevci</t>
+        </is>
+      </c>
+      <c r="C6892" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="6893">
+      <c r="A6893" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6893" t="inlineStr">
+        <is>
+          <t>Kutjevo</t>
+        </is>
+      </c>
+      <c r="C6893" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="6894">
+      <c r="A6894" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6894" t="inlineStr">
+        <is>
+          <t>Lastovo</t>
+        </is>
+      </c>
+      <c r="C6894" t="n">
+        <v>20.3</v>
+      </c>
+    </row>
+    <row r="6895">
+      <c r="A6895" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6895" t="inlineStr">
+        <is>
+          <t>Lekenik</t>
+        </is>
+      </c>
+      <c r="C6895" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="6896">
+      <c r="A6896" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6896" t="inlineStr">
+        <is>
+          <t>Ličko Lešće</t>
+        </is>
+      </c>
+      <c r="C6896" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="6897">
+      <c r="A6897" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6897" t="inlineStr">
+        <is>
+          <t>Lipik</t>
+        </is>
+      </c>
+      <c r="C6897" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="6898">
+      <c r="A6898" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6898" t="inlineStr">
+        <is>
+          <t>Makarska</t>
+        </is>
+      </c>
+      <c r="C6898" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="6899">
+      <c r="A6899" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6899" t="inlineStr">
+        <is>
+          <t>Mali Lošinj</t>
+        </is>
+      </c>
+      <c r="C6899" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="6900">
+      <c r="A6900" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6900" t="inlineStr">
+        <is>
+          <t>Ogulin</t>
+        </is>
+      </c>
+      <c r="C6900" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="6901">
+      <c r="A6901" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6901" t="inlineStr">
+        <is>
+          <t>Osijek</t>
+        </is>
+      </c>
+      <c r="C6901" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="6902">
+      <c r="A6902" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6902" t="inlineStr">
+        <is>
+          <t>Osijek-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6902" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6903">
+      <c r="A6903" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6903" t="inlineStr">
+        <is>
+          <t>Palagruža</t>
+        </is>
+      </c>
+      <c r="C6903" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="6904">
+      <c r="A6904" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6904" t="inlineStr">
+        <is>
+          <t>Parg-Čabar</t>
+        </is>
+      </c>
+      <c r="C6904" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="6905">
+      <c r="A6905" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6905" t="inlineStr">
+        <is>
+          <t>Pazin</t>
+        </is>
+      </c>
+      <c r="C6905" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6906">
+      <c r="A6906" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6906" t="inlineStr">
+        <is>
+          <t>Ploče</t>
+        </is>
+      </c>
+      <c r="C6906" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="6907">
+      <c r="A6907" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6907" t="inlineStr">
+        <is>
+          <t>Polje Čepić</t>
+        </is>
+      </c>
+      <c r="C6907" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="6908">
+      <c r="A6908" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6908" t="inlineStr">
+        <is>
+          <t>Poreč</t>
+        </is>
+      </c>
+      <c r="C6908" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="6909">
+      <c r="A6909" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6909" t="inlineStr">
+        <is>
+          <t>Požega</t>
+        </is>
+      </c>
+      <c r="C6909" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="6910">
+      <c r="A6910" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6910" t="inlineStr">
+        <is>
+          <t>Pula</t>
+        </is>
+      </c>
+      <c r="C6910" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6911">
+      <c r="A6911" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6911" t="inlineStr">
+        <is>
+          <t>Pula-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6911" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="6912">
+      <c r="A6912" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6912" t="inlineStr">
+        <is>
+          <t>RC Puntijarka</t>
+        </is>
+      </c>
+      <c r="C6912" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="6913">
+      <c r="A6913" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6913" t="inlineStr">
+        <is>
+          <t>Rab</t>
+        </is>
+      </c>
+      <c r="C6913" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="6914">
+      <c r="A6914" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6914" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C6914" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="6915">
+      <c r="A6915" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6915" t="inlineStr">
+        <is>
+          <t>Rijeka-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6915" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="6916">
+      <c r="A6916" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6916" t="inlineStr">
+        <is>
+          <t>Rovinj</t>
+        </is>
+      </c>
+      <c r="C6916" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6917">
+      <c r="A6917" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6917" t="inlineStr">
+        <is>
+          <t>Senj</t>
+        </is>
+      </c>
+      <c r="C6917" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="6918">
+      <c r="A6918" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6918" t="inlineStr">
+        <is>
+          <t>Šibenik</t>
+        </is>
+      </c>
+      <c r="C6918" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="6919">
+      <c r="A6919" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6919" t="inlineStr">
+        <is>
+          <t>Sinj</t>
+        </is>
+      </c>
+      <c r="C6919" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="6920">
+      <c r="A6920" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6920" t="inlineStr">
+        <is>
+          <t>Sisak</t>
+        </is>
+      </c>
+      <c r="C6920" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="6921">
+      <c r="A6921" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6921" t="inlineStr">
+        <is>
+          <t>Slatina</t>
+        </is>
+      </c>
+      <c r="C6921" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="6922">
+      <c r="A6922" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6922" t="inlineStr">
+        <is>
+          <t>Slavonski Brod</t>
+        </is>
+      </c>
+      <c r="C6922" t="n">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="6923">
+      <c r="A6923" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6923" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C6923" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6924">
+      <c r="A6924" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6924" t="inlineStr">
+        <is>
+          <t>Split-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6924" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="6925">
+      <c r="A6925" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6925" t="inlineStr">
+        <is>
+          <t>Sv. Ivan na pučini - svjetionik</t>
+        </is>
+      </c>
+      <c r="C6925" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6926">
+      <c r="A6926" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6926" t="inlineStr">
+        <is>
+          <t>Valpovo-Tiborjanci</t>
+        </is>
+      </c>
+      <c r="C6926" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="6927">
+      <c r="A6927" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6927" t="inlineStr">
+        <is>
+          <t>Varaždin</t>
+        </is>
+      </c>
+      <c r="C6927" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="6928">
+      <c r="A6928" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6928" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="C6928" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="6929">
+      <c r="A6929" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6929" t="inlineStr">
+        <is>
+          <t>Zadar-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6929" t="n">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="6930">
+      <c r="A6930" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6930" t="inlineStr">
+        <is>
+          <t>Zagreb-Grič</t>
+        </is>
+      </c>
+      <c r="C6930" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="6931">
+      <c r="A6931" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6931" t="inlineStr">
+        <is>
+          <t>Zagreb-Maksimir</t>
+        </is>
+      </c>
+      <c r="C6931" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="6932">
+      <c r="A6932" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6932" t="inlineStr">
+        <is>
+          <t>Zagreb-aerodrom</t>
+        </is>
+      </c>
+      <c r="C6932" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="6933">
+      <c r="A6933" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B6933" t="inlineStr">
+        <is>
+          <t>Zavižan</t>
+        </is>
+      </c>
+      <c r="C6933" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
